--- a/PVA second supplier initiative/Supplier_Capacity_Inputs.xlsx
+++ b/PVA second supplier initiative/Supplier_Capacity_Inputs.xlsx
@@ -119,7 +119,7 @@
     <t xml:space="preserve">Slaughterhouse Capacity vs Tissue Demand per Quarter</t>
   </si>
   <si>
-    <t xml:space="preserve">Net = harvested pigs (Sheet1!J16:J19 = gross kill x wtd spec yield x wtd harvest yield). Yield loss = gross - net, drawn as the pale extension of each block. Demand = tissue units consumed per quarter (Sheet1!L10:P13), assuming 1 tissue = 1 pig equivalent (per request). Capacity is flat across quarters because Sheet1 gives a single weekly kill rate (x13 wks/qtr). All cells link to Sheet1.</t>
+    <t xml:space="preserve">Net = harvested pigs (Sheet1!J16:J19 = gross kill x wtd spec yield x wtd harvest yield). Yield loss = gross - net, drawn as the hatched extension of each block. Demand = tissue units consumed per quarter (Sheet1!L10:P13), assuming 1 tissue = 1 pig equivalent (per request). Capacity is flat across quarters because Sheet1 gives a single weekly kill rate (x13 wks/qtr). All cells link to Sheet1.</t>
   </si>
   <si>
     <t xml:space="preserve">Series</t>
@@ -138,11 +138,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0%"/>
-    <numFmt numFmtId="166" formatCode="0.00%"/>
-    <numFmt numFmtId="167" formatCode="#,##0"/>
+    <numFmt numFmtId="165" formatCode="General"/>
+    <numFmt numFmtId="166" formatCode="0%"/>
+    <numFmt numFmtId="167" formatCode="0.00%"/>
+    <numFmt numFmtId="168" formatCode="#,##0"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -288,10 +289,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -300,23 +297,27 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -340,11 +341,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -374,15 +375,15 @@
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFBFBFBF"/>
-      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF8B8B8B"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FFE34948"/>
-      <rgbColor rgb="FFFAE2B3"/>
-      <rgbColor rgb="FFD9D9D9"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFE87BA4"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFBFD6F3"/>
+      <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -393,12 +394,12 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFBBE7D7"/>
+      <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFF9D2C2"/>
+      <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF2A78D6"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -406,7 +407,7 @@
       <rgbColor rgb="FFEDA100"/>
       <rgbColor rgb="FFEB6834"/>
       <rgbColor rgb="FF595959"/>
-      <rgbColor rgb="FFB3B3B3"/>
+      <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF1BAF7A"/>
       <rgbColor rgb="FF0B0B0B"/>
@@ -446,7 +447,7 @@
                 </a:solidFill>
                 <a:latin typeface="Aptos Narrow"/>
               </a:rPr>
-              <a:t>Net harvested capacity (solid) vs gross kill (pale) vs total tissue demand</a:t>
+              <a:t>Net harvested capacity (solid) vs gross kill (hatched) vs total tissue demand</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -579,9 +580,14 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="bfd6f3"/>
-            </a:solidFill>
+            <a:pattFill prst="wdUpDiag">
+              <a:fgClr>
+                <a:srgbClr val="2a78d6"/>
+              </a:fgClr>
+              <a:bgClr>
+                <a:srgbClr val="ffffff"/>
+              </a:bgClr>
+            </a:pattFill>
             <a:ln w="9360">
               <a:solidFill>
                 <a:srgbClr val="ffffff"/>
@@ -777,9 +783,14 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="f9d2c2"/>
-            </a:solidFill>
+            <a:pattFill prst="wdUpDiag">
+              <a:fgClr>
+                <a:srgbClr val="eb6834"/>
+              </a:fgClr>
+              <a:bgClr>
+                <a:srgbClr val="ffffff"/>
+              </a:bgClr>
+            </a:pattFill>
             <a:ln w="9360">
               <a:solidFill>
                 <a:srgbClr val="ffffff"/>
@@ -975,9 +986,14 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="bbe7d7"/>
-            </a:solidFill>
+            <a:pattFill prst="wdUpDiag">
+              <a:fgClr>
+                <a:srgbClr val="1baf7a"/>
+              </a:fgClr>
+              <a:bgClr>
+                <a:srgbClr val="ffffff"/>
+              </a:bgClr>
+            </a:pattFill>
             <a:ln w="9360">
               <a:solidFill>
                 <a:srgbClr val="ffffff"/>
@@ -1173,9 +1189,14 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="fae2b3"/>
-            </a:solidFill>
+            <a:pattFill prst="wdUpDiag">
+              <a:fgClr>
+                <a:srgbClr val="eda100"/>
+              </a:fgClr>
+              <a:bgClr>
+                <a:srgbClr val="ffffff"/>
+              </a:bgClr>
+            </a:pattFill>
             <a:ln w="9360">
               <a:solidFill>
                 <a:srgbClr val="ffffff"/>
@@ -1259,8 +1280,8 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="63113231"/>
-        <c:axId val="66431258"/>
+        <c:axId val="313599"/>
+        <c:axId val="20721379"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -1381,11 +1402,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="63113231"/>
-        <c:axId val="66431258"/>
+        <c:axId val="313599"/>
+        <c:axId val="20721379"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="63113231"/>
+        <c:axId val="313599"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1430,10 +1451,11 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="0">
+          <a:ln w="12600">
             <a:solidFill>
-              <a:srgbClr val="b3b3b3"/>
+              <a:srgbClr val="8b8b8b"/>
             </a:solidFill>
+            <a:round/>
           </a:ln>
         </c:spPr>
         <c:txPr>
@@ -1450,7 +1472,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66431258"/>
+        <c:crossAx val="20721379"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1458,7 +1480,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="66431258"/>
+        <c:axId val="20721379"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1466,10 +1488,11 @@
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="0">
+            <a:ln w="12600">
               <a:solidFill>
-                <a:srgbClr val="b3b3b3"/>
+                <a:srgbClr val="8b8b8b"/>
               </a:solidFill>
+              <a:round/>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
@@ -1512,10 +1535,11 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="0">
+          <a:ln w="12600">
             <a:solidFill>
-              <a:srgbClr val="b3b3b3"/>
+              <a:srgbClr val="8b8b8b"/>
             </a:solidFill>
+            <a:round/>
           </a:ln>
         </c:spPr>
         <c:txPr>
@@ -1532,7 +1556,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="63113231"/>
+        <c:crossAx val="313599"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2027,8 +2051,8 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="1142564"/>
-        <c:axId val="95739965"/>
+        <c:axId val="96558933"/>
+        <c:axId val="73157146"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2581,11 +2605,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="1142564"/>
-        <c:axId val="95739965"/>
+        <c:axId val="96558933"/>
+        <c:axId val="73157146"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1142564"/>
+        <c:axId val="96558933"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2630,10 +2654,11 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="0">
+          <a:ln w="12600">
             <a:solidFill>
-              <a:srgbClr val="b3b3b3"/>
+              <a:srgbClr val="8b8b8b"/>
             </a:solidFill>
+            <a:round/>
           </a:ln>
         </c:spPr>
         <c:txPr>
@@ -2650,7 +2675,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="95739965"/>
+        <c:crossAx val="73157146"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2658,7 +2683,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="95739965"/>
+        <c:axId val="73157146"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2666,10 +2691,11 @@
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="0">
+            <a:ln w="12600">
               <a:solidFill>
-                <a:srgbClr val="b3b3b3"/>
+                <a:srgbClr val="8b8b8b"/>
               </a:solidFill>
+              <a:round/>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
@@ -2712,10 +2738,11 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="0">
+          <a:ln w="12600">
             <a:solidFill>
-              <a:srgbClr val="b3b3b3"/>
+              <a:srgbClr val="8b8b8b"/>
             </a:solidFill>
+            <a:round/>
           </a:ln>
         </c:spPr>
         <c:txPr>
@@ -2732,7 +2759,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1142564"/>
+        <c:crossAx val="96558933"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3029,231 +3056,231 @@
   <dimension ref="C3:S23"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="27.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="16.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="27.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="16.44"/>
   </cols>
   <sheetData>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C3" s="2" t="s">
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="L3" s="1" t="n">
         <v>666501</v>
       </c>
-      <c r="M3" s="1" t="n">
+      <c r="M3" s="0" t="n">
         <v>666502</v>
       </c>
-      <c r="N3" s="1" t="n">
+      <c r="N3" s="0" t="n">
         <v>666506</v>
       </c>
-      <c r="O3" s="1" t="n">
+      <c r="O3" s="0" t="n">
         <v>666541</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C4" s="2" t="n">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C4" s="1" t="n">
         <v>666035</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I4" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N4" s="3" t="n">
+      <c r="N4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O4" s="3" t="n">
+      <c r="O4" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C5" s="2" t="s">
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="1" t="n">
         <v>320</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="1" t="n">
         <v>340</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="1" t="n">
         <v>365</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" s="1" t="n">
         <v>380</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="L5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N5" s="3" t="n">
+      <c r="N5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="O5" s="3" t="n">
+      <c r="O5" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C6" s="2" t="n">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C6" s="1" t="n">
         <v>666052</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="1" t="n">
         <v>135</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="1" t="n">
         <v>125</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="1" t="n">
         <v>125</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="I6" s="1" t="n">
         <v>128</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N6" s="3" t="n">
+      <c r="N6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O6" s="3" t="n">
+      <c r="O6" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C7" s="2" t="n">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C7" s="1" t="n">
         <v>666069</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="1" t="n">
         <v>1800</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="1" t="n">
         <v>1950</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="1" t="n">
         <v>2050</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="1" t="n">
         <v>2075</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="I7" s="1" t="n">
         <v>2050</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="L7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N7" s="3" t="n">
+      <c r="N7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O7" s="3" t="n">
+      <c r="O7" s="2" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="L9" s="2" t="s">
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="M9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="N9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="O9" s="2" t="s">
+      <c r="O9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="P9" s="2" t="s">
+      <c r="P9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="R9" s="2" t="s">
+      <c r="R9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="S9" s="2" t="s">
+      <c r="S9" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K10" s="2" t="n">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K10" s="1" t="n">
         <v>666501</v>
       </c>
-      <c r="L10" s="1" t="n">
+      <c r="L10" s="3" t="n">
         <f aca="false" t="array" ref="L10:L10">SUM(E$4:E$7*$L$4:$L$7)</f>
         <v>2970</v>
       </c>
-      <c r="M10" s="1" t="n">
+      <c r="M10" s="3" t="n">
         <f aca="false" t="array" ref="M10:M10">SUM(F$4:F$7*$L$4:$L$7)</f>
         <v>3150</v>
       </c>
-      <c r="N10" s="1" t="n">
+      <c r="N10" s="3" t="n">
         <f aca="false" t="array" ref="N10:N10">SUM(G$4:G$7*$L$4:$L$7)</f>
         <v>3320</v>
       </c>
-      <c r="O10" s="1" t="n">
+      <c r="O10" s="3" t="n">
         <f aca="false" t="array" ref="O10:O10">SUM(H$4:H$7*$L$4:$L$7)</f>
         <v>3420</v>
       </c>
-      <c r="P10" s="1" t="n">
+      <c r="P10" s="3" t="n">
         <f aca="false" t="array" ref="P10:P10">SUM(I$4:I$7*$L$4:$L$7)</f>
         <v>3446</v>
       </c>
@@ -3264,27 +3291,27 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K11" s="2" t="n">
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K11" s="1" t="n">
         <v>666502</v>
       </c>
-      <c r="L11" s="1" t="n">
+      <c r="L11" s="3" t="n">
         <f aca="false" t="array" ref="L11:L11">SUM(E$4:E$7*$M$4:$M$7)</f>
         <v>1800</v>
       </c>
-      <c r="M11" s="1" t="n">
+      <c r="M11" s="3" t="n">
         <f aca="false" t="array" ref="M11:M11">SUM(F$4:F$7*$M$4:$M$7)</f>
         <v>1950</v>
       </c>
-      <c r="N11" s="1" t="n">
+      <c r="N11" s="3" t="n">
         <f aca="false" t="array" ref="N11:N11">SUM(G$4:G$7*$M$4:$M$7)</f>
         <v>2050</v>
       </c>
-      <c r="O11" s="1" t="n">
+      <c r="O11" s="3" t="n">
         <f aca="false" t="array" ref="O11:O11">SUM(H$4:H$7*$M$4:$M$7)</f>
         <v>2075</v>
       </c>
-      <c r="P11" s="1" t="n">
+      <c r="P11" s="3" t="n">
         <f aca="false" t="array" ref="P11:P11">SUM(I$4:I$7*$M$4:$M$7)</f>
         <v>2050</v>
       </c>
@@ -3295,27 +3322,27 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K12" s="2" t="n">
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K12" s="1" t="n">
         <v>666506</v>
       </c>
-      <c r="L12" s="1" t="n">
+      <c r="L12" s="3" t="n">
         <f aca="false" t="array" ref="L12:L12">SUM(E$4:E$7*$N$4:$N$7)</f>
         <v>735</v>
       </c>
-      <c r="M12" s="1" t="n">
+      <c r="M12" s="3" t="n">
         <f aca="false" t="array" ref="M12:M12">SUM(F$4:F$7*$N$4:$N$7)</f>
         <v>760</v>
       </c>
-      <c r="N12" s="1" t="n">
+      <c r="N12" s="3" t="n">
         <f aca="false" t="array" ref="N12:N12">SUM(G$4:G$7*$N$4:$N$7)</f>
         <v>805</v>
       </c>
-      <c r="O12" s="1" t="n">
+      <c r="O12" s="3" t="n">
         <f aca="false" t="array" ref="O12:O12">SUM(H$4:H$7*$N$4:$N$7)</f>
         <v>855</v>
       </c>
-      <c r="P12" s="1" t="n">
+      <c r="P12" s="3" t="n">
         <f aca="false" t="array" ref="P12:P12">SUM(I$4:I$7*$N$4:$N$7)</f>
         <v>888</v>
       </c>
@@ -3326,27 +3353,27 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K13" s="2" t="n">
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K13" s="1" t="n">
         <v>666541</v>
       </c>
-      <c r="L13" s="1" t="n">
+      <c r="L13" s="3" t="n">
         <f aca="false" t="array" ref="L13:L13">SUM(E$4:E$7*$O$4:$O$7)</f>
         <v>1800</v>
       </c>
-      <c r="M13" s="1" t="n">
+      <c r="M13" s="3" t="n">
         <f aca="false" t="array" ref="M13:M13">SUM(F$4:F$7*$O$4:$O$7)</f>
         <v>1950</v>
       </c>
-      <c r="N13" s="1" t="n">
+      <c r="N13" s="3" t="n">
         <f aca="false" t="array" ref="N13:N13">SUM(G$4:G$7*$O$4:$O$7)</f>
         <v>2050</v>
       </c>
-      <c r="O13" s="1" t="n">
+      <c r="O13" s="3" t="n">
         <f aca="false" t="array" ref="O13:O13">SUM(H$4:H$7*$O$4:$O$7)</f>
         <v>2075</v>
       </c>
-      <c r="P13" s="1" t="n">
+      <c r="P13" s="3" t="n">
         <f aca="false" t="array" ref="P13:P13">SUM(I$4:I$7*$O$4:$O$7)</f>
         <v>2050</v>
       </c>
@@ -3357,8 +3384,8 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F14" s="1" t="n">
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F14" s="0" t="n">
         <v>13</v>
       </c>
       <c r="H14" s="5" t="s">
@@ -3368,34 +3395,34 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E15" s="1" t="s">
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E15" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" s="0" t="s">
         <v>18</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="I15" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J15" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D16" s="1" t="s">
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D16" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="1" t="n">
+      <c r="E16" s="0" t="n">
         <v>2500</v>
       </c>
-      <c r="F16" s="1" t="n">
+      <c r="F16" s="0" t="n">
         <f aca="false">E16*$F$14</f>
         <v>32500</v>
       </c>
@@ -3416,14 +3443,14 @@
         <v>17220.7857529863</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D17" s="1" t="s">
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D17" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="E17" s="1" t="n">
+      <c r="E17" s="0" t="n">
         <v>180</v>
       </c>
-      <c r="F17" s="1" t="n">
+      <c r="F17" s="0" t="n">
         <f aca="false">E17*$F$14</f>
         <v>2340</v>
       </c>
@@ -3444,14 +3471,14 @@
         <v>1239.89657421501</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D18" s="1" t="s">
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D18" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="E18" s="1" t="n">
+      <c r="E18" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="F18" s="1" t="n">
+      <c r="F18" s="0" t="n">
         <f aca="false">E18*$F$14</f>
         <v>1950</v>
       </c>
@@ -3472,14 +3499,14 @@
         <v>1033.24714517918</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D19" s="1" t="s">
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D19" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="E19" s="1" t="n">
+      <c r="E19" s="0" t="n">
         <v>400</v>
       </c>
-      <c r="F19" s="1" t="n">
+      <c r="F19" s="0" t="n">
         <f aca="false">E19*$F$14</f>
         <v>5200</v>
       </c>
@@ -3500,28 +3527,28 @@
         <v>2396.61114142236</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I22" s="1" t="s">
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I22" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="L22" s="1" t="s">
+      <c r="L22" s="0" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I23" s="1" t="s">
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I23" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="J23" s="1" t="s">
+      <c r="J23" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="K23" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="L23" s="1" t="s">
+      <c r="L23" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="M23" s="1" t="s">
+      <c r="M23" s="0" t="s">
         <v>30</v>
       </c>
     </row>

--- a/PVA second supplier initiative/Supplier_Capacity_Inputs.xlsx
+++ b/PVA second supplier initiative/Supplier_Capacity_Inputs.xlsx
@@ -5,11 +5,14 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Capacity vs Demand" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Viz 1 - Supply vs Demand" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Viz 2 - Dashboard" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Viz 3 - Capacity Funnel" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Chart Data" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="74">
   <si>
     <t xml:space="preserve">Part Number</t>
   </si>
@@ -116,16 +119,121 @@
     <t xml:space="preserve">net2</t>
   </si>
   <si>
-    <t xml:space="preserve">Slaughterhouse Capacity vs Tissue Demand per Quarter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chart 1 blocks = net capacity at spec yield (Sheet1!H16:H19); chart 2 blocks = net harvested capacity (Sheet1!J16:J19). Wider gray bars behind are context shadows: light gray tops out at total gross kill (SUM Sheet1!F16:F19 = 41,990); the darker gray band in chart 2 tops out at total spec-yield capacity (SUM Sheet1!H16:H19). Demand line = total tissue units consumed per quarter (Sheet1!L10:P13), assuming 1 tissue = 1 pig equivalent (per request). Capacity is flat across quarters because Sheet1 gives a single weekly kill rate (x13 wks/qtr). Both chart axes are fixed at 0-45,000 so the front blocks and back shadows share one scale; raise the axis max on both charts if capacities grow past it. All cells link to Sheet1.</t>
+    <t xml:space="preserve">Pig tissue supply vs demand, Q4'26-Q4'27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coverage at peak demand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net harvested capacity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peak quarterly demand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martins share of net harvested</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pigs per quarter, flat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source &amp; assumptions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supply assumes one constant weekly kill rate x 13 weeks per quarter, held flat Q4'26-Q4'27; no seasonality or downtime modeled.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demand = total tissue units across parts 666501, 666502, 666506, 666541.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross kill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net at spec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net harvested</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pig tissue supply plan - capacity vs demand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All figures in pigs per quarter. Supply is flat across quarters (single weekly kill rate x 13). Q4'26-Q4'27.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross kill capacity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net at spec yield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coverage at peak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pigs/qtr, 4 houses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supply per quarter by slaughterhouse (flat across quarters)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% of net</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tissue demand and coverage by quarter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demand (tissue units)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coverage (net / demand)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tissue supply capacity funnel, Q4'26-Q4'27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net harvested capacity / quarter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross-to-harvest yield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">flat: weekly kill rate x 13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supply by slaughterhouse (pigs per quarter)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demand by tissue part (pigs per quarter)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supply is flat: single weekly kill rate x 13 weeks per quarter. 1 tissue unit = 1 pig equivalent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chart Data — feeds the three Viz sheets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every cell links to Sheet1: gross = weekly kill x 13 wks/qtr (Sheet1!E16:F19); net @ spec yield = Sheet1!H16:H19; net harvested = Sheet1!J16:J19 (spec x harvest yields); demand = tissue units per quarter (Sheet1!L10:P13), counted at 1 tissue = 1 pig equivalent (per planning assumption). Capacity is flat across quarters because Sheet1 holds a single weekly kill rate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funnel view (stages as categories)</t>
   </si>
   <si>
     <t xml:space="preserve">Series</t>
   </si>
   <si>
     <t xml:space="preserve">Total capacity @ spec yield (pigs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tissue demand</t>
   </si>
   <si>
     <t xml:space="preserve">Total net harvested (pigs)</t>
@@ -144,14 +252,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
     <numFmt numFmtId="166" formatCode="0%"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
     <numFmt numFmtId="168" formatCode="#,##0"/>
+    <numFmt numFmtId="169" formatCode="0.0\x"/>
+    <numFmt numFmtId="170" formatCode="#,##0.0,\K"/>
+    <numFmt numFmtId="171" formatCode="[=0]0;#,##0,\K"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="36">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -183,7 +294,191 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF595959"/>
+      <name val="Aptos Narrow"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="28"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
+      <name val="Aptos Narrow"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8.5"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FF0B0B0B"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF0B0B0B"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="20"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="30"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="14"/>
+      <color rgb="FF0B0B0B"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12.5"/>
+      <color rgb="FF0B0B0B"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9.5"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF999999"/>
+      <name val="Aptos Narrow"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF404040"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="13"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="0"/>
@@ -192,6 +487,14 @@
     <font>
       <i val="true"/>
       <sz val="9"/>
+      <color rgb="FF595959"/>
+      <name val="Aptos Narrow"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
       <color rgb="FF595959"/>
       <name val="Aptos Narrow"/>
       <family val="0"/>
@@ -212,28 +515,8 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
-    <font>
-      <b val="true"/>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -246,12 +529,108 @@
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7F7F7"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="12">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thick">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thick">
+        <color rgb="FFB3B3B3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thick">
+        <color rgb="FF595959"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thick">
+        <color rgb="FF0B0B0B"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thick">
+        <color rgb="FF2A78D6"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thick">
+        <color rgb="FFEB6834"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thick">
+        <color rgb="FF1BAF7A"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thick">
+        <color rgb="FFEDA100"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -290,7 +669,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="60">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -335,23 +714,199 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="35" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="35" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -375,19 +930,19 @@
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF008300"/>
       <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF7F7F7F"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFBFBFBF"/>
-      <rgbColor rgb="FF8B8B8B"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF889AAA"/>
+      <rgbColor rgb="FFA02B93"/>
+      <rgbColor rgb="FFF7F7F7"/>
+      <rgbColor rgb="FFE7E7E7"/>
       <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FFE87BA4"/>
       <rgbColor rgb="FF0066CC"/>
       <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FF000080"/>
@@ -402,26 +957,26 @@
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFB3B3B3"/>
       <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FF8B8B8B"/>
       <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF2A78D6"/>
       <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FF4EA72E"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFEDA100"/>
       <rgbColor rgb="FFEB6834"/>
       <rgbColor rgb="FF595959"/>
-      <rgbColor rgb="FFB3B3B3"/>
+      <rgbColor rgb="FF999999"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF1BAF7A"/>
       <rgbColor rgb="FF0B0B0B"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="FFE34948"/>
+      <rgbColor rgb="FF4A3AA7"/>
+      <rgbColor rgb="FF404040"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -429,6 +984,7 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
   <chart>
     <title>
       <tx>
@@ -436,16 +992,69 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr sz="1200" b="1" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B0B0B"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>Net capacity at spec yield vs demand (total gross kill shadow behind)</a:t>
+              <a:rPr sz="1200" b="1" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B0B0B"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:rPr>
+              <a:t>Net supply at spec yield vs demand, Q4'26-Q4'27</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="7F7F7F"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="900" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="7F7F7F"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:rPr>
+              <a:t>Pigs per quarter. Spec-yield supply covers peak demand ~3.8x; gray band = gross kill (42.0K).</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.005"/>
+          <y val="0.02"/>
+        </manualLayout>
+      </layout>
+      <overlay val="0"/>
     </title>
     <plotArea>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.055"/>
+          <y val="0.17"/>
+          <w val="0.93"/>
+          <h val="0.64"/>
+        </manualLayout>
+      </layout>
       <barChart>
         <barDir val="col"/>
         <grouping val="stacked"/>
@@ -453,33 +1062,29 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <strRef>
-              <f>'Capacity vs Demand'!A15</f>
-            </strRef>
+            <v>Gross kill (context)</v>
           </tx>
           <spPr>
             <a:solidFill>
               <a:srgbClr val="D9D9D9"/>
             </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
+            <a:ln>
+              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Capacity vs Demand'!$B$4:$F$4</f>
+              <f>'Chart Data'!$B$4:$F$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Capacity vs Demand'!$B$15:$F$15</f>
+              <f>'Chart Data'!$B$15:$F$15</f>
             </numRef>
           </val>
         </ser>
-        <gapWidth val="20"/>
+        <gapWidth val="50"/>
         <overlap val="100"/>
         <axId val="10"/>
         <axId val="100"/>
@@ -492,14 +1097,81 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Capacity vs Demand'!A5</f>
+              <f>Sheet1!$D$16</f>
             </strRef>
           </tx>
           <spPr>
             <a:solidFill>
               <a:srgbClr val="2A78D6"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln w="15875">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dLbls>
+            <dLbl>
+              <idx val="0"/>
+              <numFmt formatCode="#,##0.0,&quot;K&quot;"/>
+              <dLblPos val="ctr"/>
+              <showLegendKey val="0"/>
+              <showVal val="1"/>
+              <showCatName val="0"/>
+              <showSerName val="0"/>
+              <showPercent val="0"/>
+              <showBubbleSize val="0"/>
+            </dLbl>
+            <numFmt formatCode="#,##0.0,&quot;K&quot;"/>
+            <txPr>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0">
+                    <a:solidFill>
+                      <a:srgbClr val="FFFFFF"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+                <a:endParaRPr sz="900" b="1" i="0">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:latin typeface="Aptos Narrow"/>
+                </a:endParaRPr>
+              </a:p>
+            </txPr>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+            <showBubbleSize val="0"/>
+          </dLbls>
+          <val>
+            <numRef>
+              <f>'Chart Data'!$B$5:$F$5</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>Sheet1!$D$17</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="EB6834"/>
+            </a:solidFill>
+            <a:ln w="15875">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -508,23 +1180,23 @@
           </spPr>
           <val>
             <numRef>
-              <f>'Capacity vs Demand'!$B$5:$F$5</f>
+              <f>'Chart Data'!$B$6:$F$6</f>
             </numRef>
           </val>
         </ser>
         <ser>
-          <idx val="2"/>
-          <order val="2"/>
+          <idx val="3"/>
+          <order val="3"/>
           <tx>
             <strRef>
-              <f>'Capacity vs Demand'!A6</f>
+              <f>Sheet1!$D$18</f>
             </strRef>
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EB6834"/>
+              <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln w="15875">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -533,32 +1205,7 @@
           </spPr>
           <val>
             <numRef>
-              <f>'Capacity vs Demand'!$B$6:$F$6</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="3"/>
-          <order val="3"/>
-          <tx>
-            <strRef>
-              <f>'Capacity vs Demand'!A7</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="1BAF7A"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <val>
-            <numRef>
-              <f>'Capacity vs Demand'!$B$7:$F$7</f>
+              <f>'Chart Data'!$B$7:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -567,27 +1214,69 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Capacity vs Demand'!A8</f>
+              <f>Sheet1!$D$19</f>
             </strRef>
           </tx>
           <spPr>
             <a:solidFill>
               <a:srgbClr val="EDA100"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln w="15875">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <dLbls>
+            <dLbl>
+              <idx val="0"/>
+              <numFmt formatCode="#,##0.0,&quot;K&quot;"/>
+              <dLblPos val="ctr"/>
+              <showLegendKey val="0"/>
+              <showVal val="1"/>
+              <showCatName val="0"/>
+              <showSerName val="0"/>
+              <showPercent val="0"/>
+              <showBubbleSize val="0"/>
+            </dLbl>
+            <numFmt formatCode="#,##0.0,&quot;K&quot;"/>
+            <txPr>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0">
+                    <a:solidFill>
+                      <a:srgbClr val="0B0B0B"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+                <a:endParaRPr sz="900" b="1" i="0">
+                  <a:solidFill>
+                    <a:srgbClr val="0B0B0B"/>
+                  </a:solidFill>
+                  <a:latin typeface="Aptos Narrow"/>
+                </a:endParaRPr>
+              </a:p>
+            </txPr>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+            <showBubbleSize val="0"/>
+          </dLbls>
           <val>
             <numRef>
-              <f>'Capacity vs Demand'!$B$8:$F$8</f>
+              <f>'Chart Data'!$B$8:$F$8</f>
             </numRef>
           </val>
         </ser>
-        <gapWidth val="150"/>
+        <gapWidth val="200"/>
         <overlap val="100"/>
         <axId val="10"/>
         <axId val="200"/>
@@ -598,12 +1287,10 @@
           <idx val="5"/>
           <order val="5"/>
           <tx>
-            <strRef>
-              <f>'Capacity vs Demand'!A21</f>
-            </strRef>
+            <v>Demand</v>
           </tx>
           <spPr>
-            <a:ln w="31750">
+            <a:ln w="19050" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="0B0B0B"/>
               </a:solidFill>
@@ -611,20 +1298,81 @@
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="circle"/>
-            <size val="7"/>
+            <symbol val="none"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="0B0B0B"/>
-              </a:solidFill>
               <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
+          <dPt>
+            <idx val="4"/>
+            <marker>
+              <symbol val="circle"/>
+              <size val="7"/>
+              <spPr>
+                <a:solidFill>
+                  <a:srgbClr val="0B0B0B"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:prstDash val="solid"/>
+                </a:ln>
+              </spPr>
+            </marker>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dLbls>
+            <dLbl>
+              <idx val="4"/>
+              <numFmt formatCode="#,##0.0,&quot;K&quot;"/>
+              <dLblPos val="t"/>
+              <showLegendKey val="0"/>
+              <showVal val="1"/>
+              <showCatName val="0"/>
+              <showSerName val="0"/>
+              <showPercent val="0"/>
+              <showBubbleSize val="0"/>
+            </dLbl>
+            <numFmt formatCode="#,##0.0,&quot;K&quot;"/>
+            <txPr>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0">
+                    <a:solidFill>
+                      <a:srgbClr val="FFFFFF"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+                <a:endParaRPr sz="900" b="1" i="0">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:latin typeface="Aptos Narrow"/>
+                </a:endParaRPr>
+              </a:p>
+            </txPr>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+            <showBubbleSize val="0"/>
+          </dLbls>
           <val>
             <numRef>
-              <f>'Capacity vs Demand'!$B$21:$F$21</f>
+              <f>'Chart Data'!$B$21:$F$21</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -637,24 +1385,42 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Quarter</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
+        <numFmt formatCode="@" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <spPr>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:srgbClr val="BFBFBF"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="595959"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="595959"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -665,27 +1431,52 @@
           <max val="45000"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Pigs per quarter</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="E7E7E7"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <numFmt formatCode="[=0]0;#,##0,&quot;K&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <spPr>
+          <a:ln>
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="595959"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="595959"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
+        <majorUnit val="10000"/>
       </valAx>
       <valAx>
         <axId val="200"/>
@@ -696,6 +1487,7 @@
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
+        <numFmt formatCode="[=0]0;#,##0,&quot;K&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -703,15 +1495,60 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <legendEntry>
+        <idx val="0"/>
+        <delete val="1"/>
+      </legendEntry>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.93"/>
+          <w val="0.8"/>
+          <h val="0.06"/>
+        </manualLayout>
+      </layout>
+      <overlay val="0"/>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="595959"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="900" b="0" i="0">
+            <a:solidFill>
+              <a:srgbClr val="595959"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow"/>
+          </a:endParaRPr>
+        </a:p>
+      </txPr>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
   <chart>
     <title>
       <tx>
@@ -719,16 +1556,69 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr sz="1200" b="1" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B0B0B"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>Net harvested capacity vs demand (spec-yield and gross shadows behind)</a:t>
+              <a:rPr sz="1200" b="1" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B0B0B"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:rPr>
+              <a:t>Net harvested supply vs demand, Q4'26-Q4'27</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="7F7F7F"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="900" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="7F7F7F"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:rPr>
+              <a:t>Pigs per quarter. Covers peak demand 2.6x; gray bands = gross kill (42.0K, light), net at spec (31.7K, mid).</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.005"/>
+          <y val="0.02"/>
+        </manualLayout>
+      </layout>
+      <overlay val="0"/>
     </title>
     <plotArea>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.055"/>
+          <y val="0.17"/>
+          <w val="0.93"/>
+          <h val="0.64"/>
+        </manualLayout>
+      </layout>
       <barChart>
         <barDir val="col"/>
         <grouping val="stacked"/>
@@ -736,29 +1626,25 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <strRef>
-              <f>'Capacity vs Demand'!A9</f>
-            </strRef>
+            <v>Net at spec (context)</v>
           </tx>
           <spPr>
             <a:solidFill>
               <a:srgbClr val="B3B3B3"/>
             </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
+            <a:ln>
+              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Capacity vs Demand'!$B$4:$F$4</f>
+              <f>'Chart Data'!$B$4:$F$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Capacity vs Demand'!$B$9:$F$9</f>
+              <f>'Chart Data'!$B$9:$F$9</f>
             </numRef>
           </val>
         </ser>
@@ -766,33 +1652,29 @@
           <idx val="1"/>
           <order val="1"/>
           <tx>
-            <strRef>
-              <f>'Capacity vs Demand'!A16</f>
-            </strRef>
+            <v>Spec-to-gross remainder (context)</v>
           </tx>
           <spPr>
             <a:solidFill>
               <a:srgbClr val="D9D9D9"/>
             </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
+            <a:ln>
+              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Capacity vs Demand'!$B$4:$F$4</f>
+              <f>'Chart Data'!$B$4:$F$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Capacity vs Demand'!$B$16:$F$16</f>
+              <f>'Chart Data'!$B$16:$F$16</f>
             </numRef>
           </val>
         </ser>
-        <gapWidth val="20"/>
+        <gapWidth val="50"/>
         <overlap val="100"/>
         <axId val="10"/>
         <axId val="100"/>
@@ -805,14 +1687,81 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Capacity vs Demand'!A10</f>
+              <f>Sheet1!$D$16</f>
             </strRef>
           </tx>
           <spPr>
             <a:solidFill>
               <a:srgbClr val="2A78D6"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln w="15875">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dLbls>
+            <dLbl>
+              <idx val="0"/>
+              <numFmt formatCode="#,##0.0,&quot;K&quot;"/>
+              <dLblPos val="ctr"/>
+              <showLegendKey val="0"/>
+              <showVal val="1"/>
+              <showCatName val="0"/>
+              <showSerName val="0"/>
+              <showPercent val="0"/>
+              <showBubbleSize val="0"/>
+            </dLbl>
+            <numFmt formatCode="#,##0.0,&quot;K&quot;"/>
+            <txPr>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0">
+                    <a:solidFill>
+                      <a:srgbClr val="FFFFFF"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+                <a:endParaRPr sz="900" b="1" i="0">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:latin typeface="Aptos Narrow"/>
+                </a:endParaRPr>
+              </a:p>
+            </txPr>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+            <showBubbleSize val="0"/>
+          </dLbls>
+          <val>
+            <numRef>
+              <f>'Chart Data'!$B$10:$F$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>Sheet1!$D$17</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="EB6834"/>
+            </a:solidFill>
+            <a:ln w="15875">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -821,23 +1770,23 @@
           </spPr>
           <val>
             <numRef>
-              <f>'Capacity vs Demand'!$B$10:$F$10</f>
+              <f>'Chart Data'!$B$11:$F$11</f>
             </numRef>
           </val>
         </ser>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="4"/>
+          <order val="4"/>
           <tx>
             <strRef>
-              <f>'Capacity vs Demand'!A11</f>
+              <f>Sheet1!$D$18</f>
             </strRef>
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EB6834"/>
+              <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln w="15875">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -846,23 +1795,23 @@
           </spPr>
           <val>
             <numRef>
-              <f>'Capacity vs Demand'!$B$11:$F$11</f>
+              <f>'Chart Data'!$B$12:$F$12</f>
             </numRef>
           </val>
         </ser>
         <ser>
-          <idx val="4"/>
-          <order val="4"/>
+          <idx val="5"/>
+          <order val="5"/>
           <tx>
             <strRef>
-              <f>'Capacity vs Demand'!A12</f>
+              <f>Sheet1!$D$19</f>
             </strRef>
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="1BAF7A"/>
+              <a:srgbClr val="EDA100"/>
             </a:solidFill>
-            <a:ln w="9525">
+            <a:ln w="15875">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -871,36 +1820,11 @@
           </spPr>
           <val>
             <numRef>
-              <f>'Capacity vs Demand'!$B$12:$F$12</f>
+              <f>'Chart Data'!$B$13:$F$13</f>
             </numRef>
           </val>
         </ser>
-        <ser>
-          <idx val="5"/>
-          <order val="5"/>
-          <tx>
-            <strRef>
-              <f>'Capacity vs Demand'!A13</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="EDA100"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <val>
-            <numRef>
-              <f>'Capacity vs Demand'!$B$13:$F$13</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="170"/>
+        <gapWidth val="200"/>
         <overlap val="100"/>
         <axId val="10"/>
         <axId val="200"/>
@@ -911,12 +1835,10 @@
           <idx val="6"/>
           <order val="6"/>
           <tx>
-            <strRef>
-              <f>'Capacity vs Demand'!A21</f>
-            </strRef>
+            <v>Demand</v>
           </tx>
           <spPr>
-            <a:ln w="31750">
+            <a:ln w="19050" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="0B0B0B"/>
               </a:solidFill>
@@ -924,20 +1846,81 @@
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="circle"/>
-            <size val="7"/>
+            <symbol val="none"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="0B0B0B"/>
-              </a:solidFill>
               <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
+          <dPt>
+            <idx val="4"/>
+            <marker>
+              <symbol val="circle"/>
+              <size val="7"/>
+              <spPr>
+                <a:solidFill>
+                  <a:srgbClr val="0B0B0B"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:prstDash val="solid"/>
+                </a:ln>
+              </spPr>
+            </marker>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dLbls>
+            <dLbl>
+              <idx val="4"/>
+              <numFmt formatCode="#,##0.0,&quot;K&quot;"/>
+              <dLblPos val="t"/>
+              <showLegendKey val="0"/>
+              <showVal val="1"/>
+              <showCatName val="0"/>
+              <showSerName val="0"/>
+              <showPercent val="0"/>
+              <showBubbleSize val="0"/>
+            </dLbl>
+            <numFmt formatCode="#,##0.0,&quot;K&quot;"/>
+            <txPr>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0">
+                    <a:solidFill>
+                      <a:srgbClr val="FFFFFF"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+                <a:endParaRPr sz="900" b="1" i="0">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:latin typeface="Aptos Narrow"/>
+                </a:endParaRPr>
+              </a:p>
+            </txPr>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+            <showBubbleSize val="0"/>
+          </dLbls>
           <val>
             <numRef>
-              <f>'Capacity vs Demand'!$B$21:$F$21</f>
+              <f>'Chart Data'!$B$21:$F$21</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -950,24 +1933,42 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Quarter</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
+        <numFmt formatCode="@" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <spPr>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:srgbClr val="BFBFBF"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="595959"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="595959"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -978,27 +1979,52 @@
           <max val="45000"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Pigs per quarter</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="E7E7E7"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <numFmt formatCode="[=0]0;#,##0,&quot;K&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <spPr>
+          <a:ln>
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="595959"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="595959"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
+        <majorUnit val="10000"/>
       </valAx>
       <valAx>
         <axId val="200"/>
@@ -1009,6 +2035,7 @@
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
+        <numFmt formatCode="[=0]0;#,##0,&quot;K&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -1016,10 +2043,1987 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <legendEntry>
+        <idx val="0"/>
+        <delete val="1"/>
+      </legendEntry>
+      <legendEntry>
+        <idx val="1"/>
+        <delete val="1"/>
+      </legendEntry>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.93"/>
+          <w val="0.8"/>
+          <h val="0.06"/>
+        </manualLayout>
+      </layout>
+      <overlay val="0"/>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="595959"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="900" b="0" i="0">
+            <a:solidFill>
+              <a:srgbClr val="595959"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow"/>
+          </a:endParaRPr>
+        </a:p>
+      </txPr>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B0B0B"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B0B0B"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:rPr>
+              <a:t>Harvest capacity vs tissue demand by quarter</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="950" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="7F7F7F"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="950" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="7F7F7F"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:rPr>
+              <a:t>Pigs per quarter, Q4'26-Q4'27. Blocks = net harvested; line = demand</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="950" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="7F7F7F"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="950" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="7F7F7F"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:rPr>
+              <a:t>Gray bands: net at spec (31,733) and gross kill (41,990)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.005"/>
+          <y val="0.02"/>
+        </manualLayout>
+      </layout>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.055"/>
+          <y val="0.2"/>
+          <w val="0.93"/>
+          <h val="0.6"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Net at spec (context)</v>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="B3B3B3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart Data'!$B$4:$F$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart Data'!$B$9:$F$9</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Gross above spec (context)</v>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="D9D9D9"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart Data'!$B$4:$F$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart Data'!$B$16:$F$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="40"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>Sheet1!$D$16</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2A78D6"/>
+            </a:solidFill>
+            <a:ln w="15875">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dLbls>
+            <dLbl>
+              <idx val="0"/>
+              <numFmt formatCode="#,##0"/>
+              <dLblPos val="ctr"/>
+              <showLegendKey val="0"/>
+              <showVal val="1"/>
+              <showCatName val="0"/>
+              <showSerName val="0"/>
+              <showPercent val="0"/>
+              <showBubbleSize val="0"/>
+            </dLbl>
+            <numFmt formatCode="#,##0"/>
+            <txPr>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0">
+                    <a:solidFill>
+                      <a:srgbClr val="FFFFFF"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+                <a:endParaRPr sz="1000" b="1" i="0">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:latin typeface="Aptos Narrow"/>
+                </a:endParaRPr>
+              </a:p>
+            </txPr>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+            <showBubbleSize val="0"/>
+          </dLbls>
+          <val>
+            <numRef>
+              <f>'Chart Data'!$B$10:$F$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>Sheet1!$D$17</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="EB6834"/>
+            </a:solidFill>
+            <a:ln w="15875">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <val>
+            <numRef>
+              <f>'Chart Data'!$B$11:$F$11</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>Sheet1!$D$18</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="1BAF7A"/>
+            </a:solidFill>
+            <a:ln w="15875">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <val>
+            <numRef>
+              <f>'Chart Data'!$B$12:$F$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>Sheet1!$D$19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="EDA100"/>
+            </a:solidFill>
+            <a:ln w="15875">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <val>
+            <numRef>
+              <f>'Chart Data'!$B$13:$F$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="120"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="200"/>
+      </barChart>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <v>Demand</v>
+          </tx>
+          <spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="0B0B0B"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dPt>
+            <idx val="4"/>
+            <marker>
+              <symbol val="circle"/>
+              <size val="7"/>
+              <spPr>
+                <a:solidFill>
+                  <a:srgbClr val="0B0B0B"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:prstDash val="solid"/>
+                </a:ln>
+              </spPr>
+            </marker>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <val>
+            <numRef>
+              <f>'Chart Data'!$B$21:$F$21</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="200"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="@" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <spPr>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:srgbClr val="BFBFBF"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="595959"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="595959"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="45000"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="E7E7E7"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <spPr>
+          <a:ln>
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="595959"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="595959"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+        <majorUnit val="10000"/>
+      </valAx>
+      <valAx>
+        <axId val="200"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="45000"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <legendEntry>
+        <idx val="0"/>
+        <delete val="1"/>
+      </legendEntry>
+      <legendEntry>
+        <idx val="1"/>
+        <delete val="1"/>
+      </legendEntry>
+      <overlay val="0"/>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="595959"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="900" b="0" i="0">
+            <a:solidFill>
+              <a:srgbClr val="595959"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow"/>
+          </a:endParaRPr>
+        </a:p>
+      </txPr>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1250" b="1" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B0B0B"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1250" b="1" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B0B0B"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:rPr>
+              <a:t>Zoom: demand vs net harvested capacity</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="7F7F7F"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="900" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="7F7F7F"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:rPr>
+              <a:t>Same data, y-axis capped at 25K; gray levels sit above</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.005"/>
+          <y val="0.02"/>
+        </manualLayout>
+      </layout>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.09"/>
+          <y val="0.2"/>
+          <w val="0.89"/>
+          <h val="0.6"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>Sheet1!$D$16</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2A78D6"/>
+            </a:solidFill>
+            <a:ln w="15875">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dLbls>
+            <dLbl>
+              <idx val="0"/>
+              <numFmt formatCode="#,##0"/>
+              <dLblPos val="ctr"/>
+              <showLegendKey val="0"/>
+              <showVal val="1"/>
+              <showCatName val="0"/>
+              <showSerName val="0"/>
+              <showPercent val="0"/>
+              <showBubbleSize val="0"/>
+            </dLbl>
+            <numFmt formatCode="#,##0"/>
+            <txPr>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0">
+                    <a:solidFill>
+                      <a:srgbClr val="FFFFFF"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+                <a:endParaRPr sz="1000" b="1" i="0">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:latin typeface="Aptos Narrow"/>
+                </a:endParaRPr>
+              </a:p>
+            </txPr>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+            <showBubbleSize val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Chart Data'!$B$4:$F$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart Data'!$B$10:$F$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>Sheet1!$D$17</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="EB6834"/>
+            </a:solidFill>
+            <a:ln w="15875">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart Data'!$B$4:$F$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart Data'!$B$11:$F$11</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>Sheet1!$D$18</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="1BAF7A"/>
+            </a:solidFill>
+            <a:ln w="15875">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart Data'!$B$4:$F$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart Data'!$B$12:$F$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>Sheet1!$D$19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="EDA100"/>
+            </a:solidFill>
+            <a:ln w="15875">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart Data'!$B$4:$F$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart Data'!$B$13:$F$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="120"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <v>Demand</v>
+          </tx>
+          <spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="0B0B0B"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dPt>
+            <idx val="4"/>
+            <marker>
+              <symbol val="circle"/>
+              <size val="7"/>
+              <spPr>
+                <a:solidFill>
+                  <a:srgbClr val="0B0B0B"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:prstDash val="solid"/>
+                </a:ln>
+              </spPr>
+            </marker>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dLbls>
+            <dLbl>
+              <idx val="4"/>
+              <numFmt formatCode="#,##0"/>
+              <dLblPos val="t"/>
+              <showLegendKey val="0"/>
+              <showVal val="1"/>
+              <showCatName val="0"/>
+              <showSerName val="0"/>
+              <showPercent val="0"/>
+              <showBubbleSize val="0"/>
+            </dLbl>
+            <numFmt formatCode="#,##0"/>
+            <txPr>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="950" b="1" i="0">
+                    <a:solidFill>
+                      <a:srgbClr val="FFFFFF"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+                <a:endParaRPr sz="950" b="1" i="0">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:latin typeface="Aptos Narrow"/>
+                </a:endParaRPr>
+              </a:p>
+            </txPr>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+            <showBubbleSize val="0"/>
+          </dLbls>
+          <val>
+            <numRef>
+              <f>'Chart Data'!$B$21:$F$21</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="@" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <spPr>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:srgbClr val="BFBFBF"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="595959"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="595959"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="25000"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="E7E7E7"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <spPr>
+          <a:ln>
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="595959"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="595959"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+        <majorUnit val="5000"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <overlay val="0"/>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="595959"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="900" b="0" i="0">
+            <a:solidFill>
+              <a:srgbClr val="595959"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow"/>
+          </a:endParaRPr>
+        </a:p>
+      </txPr>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="1" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B0B0B"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1200" b="1" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B0B0B"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:rPr>
+              <a:t>Capacity funnel vs peak demand</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="7F7F7F"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="900" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="7F7F7F"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:rPr>
+              <a:t>Pigs per quarter by slaughterhouse, flat; demand bar = Q4'27 peak.</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.005"/>
+          <y val="0.02"/>
+        </manualLayout>
+      </layout>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.055"/>
+          <y val="0.18"/>
+          <w val="0.93"/>
+          <h val="0.58"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>Sheet1!$D$16</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2A78D6"/>
+            </a:solidFill>
+            <a:ln w="15875">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dLbls>
+            <numFmt formatCode="#,##0"/>
+            <txPr>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0">
+                    <a:solidFill>
+                      <a:srgbClr val="FFFFFF"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+                <a:endParaRPr sz="900" b="1" i="0">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:latin typeface="Aptos Narrow"/>
+                </a:endParaRPr>
+              </a:p>
+            </txPr>
+            <dLblPos val="ctr"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+            <showBubbleSize val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Chart Data'!$I$4:$L$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart Data'!$I$5:$L$5</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>Sheet1!$D$17</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="EB6834"/>
+            </a:solidFill>
+            <a:ln w="15875">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart Data'!$I$4:$L$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart Data'!$I$6:$L$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>Sheet1!$D$18</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="1BAF7A"/>
+            </a:solidFill>
+            <a:ln w="15875">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart Data'!$I$4:$L$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart Data'!$I$7:$L$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>Sheet1!$D$19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="EDA100"/>
+            </a:solidFill>
+            <a:ln w="15875">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart Data'!$I$4:$L$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart Data'!$I$8:$L$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Chart Data'!$H$9</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="0B0B0B"/>
+            </a:solidFill>
+            <a:ln w="15875">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dLbls>
+            <numFmt formatCode="#,##0"/>
+            <txPr>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0">
+                    <a:solidFill>
+                      <a:srgbClr val="FFFFFF"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+                <a:endParaRPr sz="900" b="1" i="0">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:latin typeface="Aptos Narrow"/>
+                </a:endParaRPr>
+              </a:p>
+            </txPr>
+            <dLblPos val="ctr"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+            <showBubbleSize val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Chart Data'!$I$4:$L$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart Data'!$I$9:$L$9</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="120"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="@" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <spPr>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:srgbClr val="BFBFBF"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="595959"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="595959"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="45000"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="E7E7E7"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <spPr>
+          <a:ln>
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="595959"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="595959"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+        <majorUnit val="10000"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <overlay val="0"/>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="595959"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="900" b="0" i="0">
+            <a:solidFill>
+              <a:srgbClr val="595959"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow"/>
+          </a:endParaRPr>
+        </a:p>
+      </txPr>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="1" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B0B0B"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1200" b="1" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B0B0B"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:rPr>
+              <a:t>Tissue demand by part vs harvested capacity</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="7F7F7F"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="900" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="7F7F7F"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:rPr>
+              <a:t>Pigs per quarter; gray line = net harvested capacity (21,891/qtr).</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.005"/>
+          <y val="0.02"/>
+        </manualLayout>
+      </layout>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.055"/>
+          <y val="0.18"/>
+          <w val="0.93"/>
+          <h val="0.58"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>Sheet1!$K$10</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="E87BA4"/>
+            </a:solidFill>
+            <a:ln w="15875">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart Data'!$B$4:$F$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart Data'!$B$17:$F$17</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>Sheet1!$K$11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="008300"/>
+            </a:solidFill>
+            <a:ln w="15875">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart Data'!$B$4:$F$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart Data'!$B$18:$F$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>Sheet1!$K$12</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="4A3AA7"/>
+            </a:solidFill>
+            <a:ln w="15875">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart Data'!$B$4:$F$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart Data'!$B$19:$F$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>Sheet1!$K$13</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="E34948"/>
+            </a:solidFill>
+            <a:ln w="15875">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart Data'!$B$4:$F$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart Data'!$B$20:$F$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="100"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <v>Net harvested capacity</v>
+          </tx>
+          <spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="999999"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dPt>
+            <idx val="4"/>
+            <marker>
+              <symbol val="circle"/>
+              <size val="6"/>
+              <spPr>
+                <a:solidFill>
+                  <a:srgbClr val="999999"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:prstDash val="solid"/>
+                </a:ln>
+              </spPr>
+            </marker>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dLbls>
+            <dLbl>
+              <idx val="4"/>
+              <numFmt formatCode="#,##0"/>
+              <dLblPos val="t"/>
+              <showLegendKey val="0"/>
+              <showVal val="1"/>
+              <showCatName val="0"/>
+              <showSerName val="0"/>
+              <showPercent val="0"/>
+              <showBubbleSize val="0"/>
+            </dLbl>
+            <numFmt formatCode="#,##0"/>
+            <txPr>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0">
+                    <a:solidFill>
+                      <a:srgbClr val="595959"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+                <a:endParaRPr sz="900" b="1" i="0">
+                  <a:solidFill>
+                    <a:srgbClr val="595959"/>
+                  </a:solidFill>
+                  <a:latin typeface="Aptos Narrow"/>
+                </a:endParaRPr>
+              </a:p>
+            </txPr>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+            <showBubbleSize val="0"/>
+          </dLbls>
+          <val>
+            <numRef>
+              <f>'Chart Data'!$B$14:$F$14</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <v>Demand total</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <numFmt formatCode="#,##0"/>
+            <txPr>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0">
+                    <a:solidFill>
+                      <a:srgbClr val="404040"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+                <a:endParaRPr sz="900" b="0" i="0">
+                  <a:solidFill>
+                    <a:srgbClr val="404040"/>
+                  </a:solidFill>
+                  <a:latin typeface="Aptos Narrow"/>
+                </a:endParaRPr>
+              </a:p>
+            </txPr>
+            <dLblPos val="t"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+            <showBubbleSize val="0"/>
+          </dLbls>
+          <val>
+            <numRef>
+              <f>'Chart Data'!$B$21:$F$21</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="@" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <spPr>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:srgbClr val="BFBFBF"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="595959"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="595959"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="24000"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="E7E7E7"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <spPr>
+          <a:ln>
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="595959"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="595959"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+        <majorUnit val="4000"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <legendEntry>
+        <idx val="4"/>
+        <delete val="1"/>
+      </legendEntry>
+      <legendEntry>
+        <idx val="5"/>
+        <delete val="1"/>
+      </legendEntry>
+      <overlay val="0"/>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="595959"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="900" b="0" i="0">
+            <a:solidFill>
+              <a:srgbClr val="595959"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow"/>
+          </a:endParaRPr>
+        </a:p>
+      </txPr>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -1027,16 +4031,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>160560</xdr:rowOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>130680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>610920</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>56880</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>189720</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>100440</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1044,8 +4048,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="4381560"/>
-        <a:ext cx="10799640" cy="5039640"/>
+        <a:off x="177840" y="1838160"/>
+        <a:ext cx="8279640" cy="3779640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1057,16 +4061,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>160920</xdr:rowOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>130680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>610920</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>56880</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>189720</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>100440</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1074,8 +4078,138 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="9906120"/>
-        <a:ext cx="10799640" cy="5039640"/>
+        <a:off x="177840" y="6029280"/>
+        <a:ext cx="8279640" cy="3779640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>131040</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1492560</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>79560</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="177840" y="1695600"/>
+        <a:ext cx="5759640" cy="4139640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>131040</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>1826280</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>79560</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="8712360" y="1695600"/>
+        <a:ext cx="3959640" cy="4139640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>130680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>592560</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>110880</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="177840" y="1647720"/>
+        <a:ext cx="4859640" cy="3599640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>130680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>599040</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>110880</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="8356680" y="1647720"/>
+        <a:ext cx="5399640" cy="3599640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1778,485 +4912,216 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF2A78D6"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="B2:H67"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="9" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="10" t="str">
+        <f aca="false">"Net harvested capacity covers peak quarterly demand "&amp;TEXT('Chart Data'!B14/MAX('Chart Data'!B21:F21),"0.0")&amp;"x; Martins carries "&amp;TEXT('Chart Data'!B10/'Chart Data'!B14,"0%")&amp;" of net supply."</f>
+        <v>Net harvested capacity covers peak quarterly demand 2.6x; Martins carries 79% of net supply.</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="11" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
+      <c r="D5" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="12" t="str">
-        <f aca="false">Sheet1!L9</f>
-        <v>Q4'26</v>
-      </c>
-      <c r="C4" s="12" t="str">
-        <f aca="false">Sheet1!M9</f>
-        <v>Q1'27</v>
-      </c>
-      <c r="D4" s="12" t="str">
-        <f aca="false">Sheet1!N9</f>
-        <v>Q2'27</v>
-      </c>
-      <c r="E4" s="12" t="str">
-        <f aca="false">Sheet1!O9</f>
-        <v>Q3'27</v>
-      </c>
-      <c r="F4" s="12" t="str">
-        <f aca="false">Sheet1!P9</f>
-        <v>Q4'27</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="str">
-        <f aca="false">Sheet1!$D$16&amp;" (net, spec yield)"</f>
-        <v>Martins (net, spec yield)</v>
-      </c>
-      <c r="B5" s="14" t="n">
-        <f aca="false">Sheet1!$H$16</f>
+      <c r="F5" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="12" t="n">
+        <f aca="false">'Chart Data'!B14/MAX('Chart Data'!B21:F21)</f>
+        <v>2.59551109957349</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <f aca="false">'Chart Data'!B14</f>
+        <v>21890.5406138028</v>
+      </c>
+      <c r="F6" s="13" t="n">
+        <f aca="false">MAX('Chart Data'!B21:F21)</f>
+        <v>8434</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <f aca="false">'Chart Data'!B10/'Chart Data'!B14</f>
+        <v>0.786677042691578</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="15" t="str">
+        <f aca="false">TEXT('Chart Data'!B14/'Chart Data'!B21,"0.0")&amp;"x at "&amp;'Chart Data'!B4</f>
+        <v>3.0x at Q4'26</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="15" t="str">
+        <f aca="false">'Chart Data'!F4&amp;", +"&amp;TEXT(MAX('Chart Data'!B21:F21)/'Chart Data'!B21-1,"0%")&amp;" vs "&amp;'Chart Data'!B4</f>
+        <v>Q4'27, +15% vs Q4'26</v>
+      </c>
+      <c r="H7" s="15" t="str">
+        <f aca="false">TEXT('Chart Data'!B10,"#,##0.0,")&amp;"K of "&amp;TEXT('Chart Data'!B14,"#,##0.0,")&amp;"K per qtr"</f>
+        <v>17.2K of 21.9K per qtr</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="15" t="str">
+        <f aca="false">"Net at spec = gross kill x spec yield ("&amp;TEXT('Chart Data'!B9/'Chart Data'!B15,"0%")&amp;"); net harvested = net at spec x harvest yield ("&amp;TEXT('Chart Data'!B14/'Chart Data'!B9,"0%")&amp;"). 1 tissue unit = 1 pig equivalent."</f>
+        <v>Net at spec = gross kill x spec yield (76%); net harvested = net at spec x harvest yield (69%). 1 tissue unit = 1 pig equivalent.</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B59" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C59" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D59" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="E59" s="18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="19" t="str">
+        <f aca="false">Sheet1!$D$16</f>
+        <v>Martins</v>
+      </c>
+      <c r="C60" s="20" t="n">
+        <f aca="false">'Chart Data'!B22</f>
+        <v>32500</v>
+      </c>
+      <c r="D60" s="20" t="n">
+        <f aca="false">'Chart Data'!B5</f>
         <v>24963.6036960986</v>
       </c>
-      <c r="C5" s="14" t="n">
-        <f aca="false">Sheet1!$H$16</f>
-        <v>24963.6036960986</v>
-      </c>
-      <c r="D5" s="14" t="n">
-        <f aca="false">Sheet1!$H$16</f>
-        <v>24963.6036960986</v>
-      </c>
-      <c r="E5" s="14" t="n">
-        <f aca="false">Sheet1!$H$16</f>
-        <v>24963.6036960986</v>
-      </c>
-      <c r="F5" s="14" t="n">
-        <f aca="false">Sheet1!$H$16</f>
-        <v>24963.6036960986</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="str">
-        <f aca="false">Sheet1!$D$17&amp;" (net, spec yield)"</f>
-        <v>Nahunta (net, spec yield)</v>
-      </c>
-      <c r="B6" s="14" t="n">
-        <f aca="false">Sheet1!$H$17</f>
+      <c r="E60" s="20" t="n">
+        <f aca="false">'Chart Data'!B10</f>
+        <v>17220.7857529863</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="19" t="str">
+        <f aca="false">Sheet1!$D$17</f>
+        <v>Nahunta</v>
+      </c>
+      <c r="C61" s="20" t="n">
+        <f aca="false">'Chart Data'!B23</f>
+        <v>2340</v>
+      </c>
+      <c r="D61" s="20" t="n">
+        <f aca="false">'Chart Data'!B6</f>
         <v>1797.3794661191</v>
       </c>
-      <c r="C6" s="14" t="n">
-        <f aca="false">Sheet1!$H$17</f>
-        <v>1797.3794661191</v>
-      </c>
-      <c r="D6" s="14" t="n">
-        <f aca="false">Sheet1!$H$17</f>
-        <v>1797.3794661191</v>
-      </c>
-      <c r="E6" s="14" t="n">
-        <f aca="false">Sheet1!$H$17</f>
-        <v>1797.3794661191</v>
-      </c>
-      <c r="F6" s="14" t="n">
-        <f aca="false">Sheet1!$H$17</f>
-        <v>1797.3794661191</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="str">
-        <f aca="false">Sheet1!$D$18&amp;" (net, spec yield)"</f>
-        <v>Customs (net, spec yield)</v>
-      </c>
-      <c r="B7" s="14" t="n">
-        <f aca="false">Sheet1!$H$18</f>
+      <c r="E61" s="20" t="n">
+        <f aca="false">'Chart Data'!B11</f>
+        <v>1239.89657421501</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="19" t="str">
+        <f aca="false">Sheet1!$D$18</f>
+        <v>Customs</v>
+      </c>
+      <c r="C62" s="20" t="n">
+        <f aca="false">'Chart Data'!B24</f>
+        <v>1950</v>
+      </c>
+      <c r="D62" s="20" t="n">
+        <f aca="false">'Chart Data'!B7</f>
         <v>1497.81622176591</v>
       </c>
-      <c r="C7" s="14" t="n">
-        <f aca="false">Sheet1!$H$18</f>
-        <v>1497.81622176591</v>
-      </c>
-      <c r="D7" s="14" t="n">
-        <f aca="false">Sheet1!$H$18</f>
-        <v>1497.81622176591</v>
-      </c>
-      <c r="E7" s="14" t="n">
-        <f aca="false">Sheet1!$H$18</f>
-        <v>1497.81622176591</v>
-      </c>
-      <c r="F7" s="14" t="n">
-        <f aca="false">Sheet1!$H$18</f>
-        <v>1497.81622176591</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="str">
-        <f aca="false">Sheet1!$D$19&amp;" (net, spec yield)"</f>
-        <v>Parks (net, spec yield)</v>
-      </c>
-      <c r="B8" s="14" t="n">
-        <f aca="false">Sheet1!$H$19</f>
+      <c r="E62" s="20" t="n">
+        <f aca="false">'Chart Data'!B12</f>
+        <v>1033.24714517918</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="21" t="str">
+        <f aca="false">Sheet1!$D$19</f>
+        <v>Parks</v>
+      </c>
+      <c r="C63" s="22" t="n">
+        <f aca="false">'Chart Data'!B25</f>
+        <v>5200</v>
+      </c>
+      <c r="D63" s="22" t="n">
+        <f aca="false">'Chart Data'!B8</f>
         <v>3474.17659137577</v>
       </c>
-      <c r="C8" s="14" t="n">
-        <f aca="false">Sheet1!$H$19</f>
-        <v>3474.17659137577</v>
-      </c>
-      <c r="D8" s="14" t="n">
-        <f aca="false">Sheet1!$H$19</f>
-        <v>3474.17659137577</v>
-      </c>
-      <c r="E8" s="14" t="n">
-        <f aca="false">Sheet1!$H$19</f>
-        <v>3474.17659137577</v>
-      </c>
-      <c r="F8" s="14" t="n">
-        <f aca="false">Sheet1!$H$19</f>
-        <v>3474.17659137577</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="15" t="n">
-        <f aca="false">SUM(B5:B8)</f>
+      <c r="E63" s="22" t="n">
+        <f aca="false">'Chart Data'!B13</f>
+        <v>2396.61114142236</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="C64" s="24" t="n">
+        <f aca="false">'Chart Data'!B15</f>
+        <v>41990</v>
+      </c>
+      <c r="D64" s="24" t="n">
+        <f aca="false">'Chart Data'!B9</f>
         <v>31732.9759753593</v>
       </c>
-      <c r="C9" s="15" t="n">
-        <f aca="false">SUM(C5:C8)</f>
-        <v>31732.9759753593</v>
-      </c>
-      <c r="D9" s="15" t="n">
-        <f aca="false">SUM(D5:D8)</f>
-        <v>31732.9759753593</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <f aca="false">SUM(E5:E8)</f>
-        <v>31732.9759753593</v>
-      </c>
-      <c r="F9" s="15" t="n">
-        <f aca="false">SUM(F5:F8)</f>
-        <v>31732.9759753593</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="str">
-        <f aca="false">Sheet1!$D$16&amp;" (net harvested)"</f>
-        <v>Martins (net harvested)</v>
-      </c>
-      <c r="B10" s="14" t="n">
-        <f aca="false">Sheet1!$J$16</f>
-        <v>17220.7857529863</v>
-      </c>
-      <c r="C10" s="14" t="n">
-        <f aca="false">Sheet1!$J$16</f>
-        <v>17220.7857529863</v>
-      </c>
-      <c r="D10" s="14" t="n">
-        <f aca="false">Sheet1!$J$16</f>
-        <v>17220.7857529863</v>
-      </c>
-      <c r="E10" s="14" t="n">
-        <f aca="false">Sheet1!$J$16</f>
-        <v>17220.7857529863</v>
-      </c>
-      <c r="F10" s="14" t="n">
-        <f aca="false">Sheet1!$J$16</f>
-        <v>17220.7857529863</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="str">
-        <f aca="false">Sheet1!$D$17&amp;" (net harvested)"</f>
-        <v>Nahunta (net harvested)</v>
-      </c>
-      <c r="B11" s="14" t="n">
-        <f aca="false">Sheet1!$J$17</f>
-        <v>1239.89657421501</v>
-      </c>
-      <c r="C11" s="14" t="n">
-        <f aca="false">Sheet1!$J$17</f>
-        <v>1239.89657421501</v>
-      </c>
-      <c r="D11" s="14" t="n">
-        <f aca="false">Sheet1!$J$17</f>
-        <v>1239.89657421501</v>
-      </c>
-      <c r="E11" s="14" t="n">
-        <f aca="false">Sheet1!$J$17</f>
-        <v>1239.89657421501</v>
-      </c>
-      <c r="F11" s="14" t="n">
-        <f aca="false">Sheet1!$J$17</f>
-        <v>1239.89657421501</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="str">
-        <f aca="false">Sheet1!$D$18&amp;" (net harvested)"</f>
-        <v>Customs (net harvested)</v>
-      </c>
-      <c r="B12" s="14" t="n">
-        <f aca="false">Sheet1!$J$18</f>
-        <v>1033.24714517918</v>
-      </c>
-      <c r="C12" s="14" t="n">
-        <f aca="false">Sheet1!$J$18</f>
-        <v>1033.24714517918</v>
-      </c>
-      <c r="D12" s="14" t="n">
-        <f aca="false">Sheet1!$J$18</f>
-        <v>1033.24714517918</v>
-      </c>
-      <c r="E12" s="14" t="n">
-        <f aca="false">Sheet1!$J$18</f>
-        <v>1033.24714517918</v>
-      </c>
-      <c r="F12" s="14" t="n">
-        <f aca="false">Sheet1!$J$18</f>
-        <v>1033.24714517918</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="str">
-        <f aca="false">Sheet1!$D$19&amp;" (net harvested)"</f>
-        <v>Parks (net harvested)</v>
-      </c>
-      <c r="B13" s="14" t="n">
-        <f aca="false">Sheet1!$J$19</f>
-        <v>2396.61114142236</v>
-      </c>
-      <c r="C13" s="14" t="n">
-        <f aca="false">Sheet1!$J$19</f>
-        <v>2396.61114142236</v>
-      </c>
-      <c r="D13" s="14" t="n">
-        <f aca="false">Sheet1!$J$19</f>
-        <v>2396.61114142236</v>
-      </c>
-      <c r="E13" s="14" t="n">
-        <f aca="false">Sheet1!$J$19</f>
-        <v>2396.61114142236</v>
-      </c>
-      <c r="F13" s="14" t="n">
-        <f aca="false">Sheet1!$J$19</f>
-        <v>2396.61114142236</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="15" t="n">
-        <f aca="false">SUM(B10:B13)</f>
+      <c r="E64" s="24" t="n">
+        <f aca="false">'Chart Data'!B14</f>
         <v>21890.5406138028</v>
       </c>
-      <c r="C14" s="15" t="n">
-        <f aca="false">SUM(C10:C13)</f>
-        <v>21890.5406138028</v>
-      </c>
-      <c r="D14" s="15" t="n">
-        <f aca="false">SUM(D10:D13)</f>
-        <v>21890.5406138028</v>
-      </c>
-      <c r="E14" s="15" t="n">
-        <f aca="false">SUM(E10:E13)</f>
-        <v>21890.5406138028</v>
-      </c>
-      <c r="F14" s="15" t="n">
-        <f aca="false">SUM(F10:F13)</f>
-        <v>21890.5406138028</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="15" t="n">
-        <f aca="false">SUM(Sheet1!$F$16:$F$19)</f>
-        <v>41990</v>
-      </c>
-      <c r="C15" s="15" t="n">
-        <f aca="false">SUM(Sheet1!$F$16:$F$19)</f>
-        <v>41990</v>
-      </c>
-      <c r="D15" s="15" t="n">
-        <f aca="false">SUM(Sheet1!$F$16:$F$19)</f>
-        <v>41990</v>
-      </c>
-      <c r="E15" s="15" t="n">
-        <f aca="false">SUM(Sheet1!$F$16:$F$19)</f>
-        <v>41990</v>
-      </c>
-      <c r="F15" s="15" t="n">
-        <f aca="false">SUM(Sheet1!$F$16:$F$19)</f>
-        <v>41990</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="14" t="n">
-        <f aca="false">B15-B9</f>
-        <v>10257.0240246407</v>
-      </c>
-      <c r="C16" s="14" t="n">
-        <f aca="false">C15-C9</f>
-        <v>10257.0240246407</v>
-      </c>
-      <c r="D16" s="14" t="n">
-        <f aca="false">D15-D9</f>
-        <v>10257.0240246407</v>
-      </c>
-      <c r="E16" s="14" t="n">
-        <f aca="false">E15-E9</f>
-        <v>10257.0240246407</v>
-      </c>
-      <c r="F16" s="14" t="n">
-        <f aca="false">F15-F9</f>
-        <v>10257.0240246407</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="str">
-        <f aca="false">"Demand "&amp;Sheet1!$K$10</f>
-        <v>Demand 666501</v>
-      </c>
-      <c r="B17" s="14" t="n">
-        <f aca="false">Sheet1!L10</f>
-        <v>2970</v>
-      </c>
-      <c r="C17" s="14" t="n">
-        <f aca="false">Sheet1!M10</f>
-        <v>3150</v>
-      </c>
-      <c r="D17" s="14" t="n">
-        <f aca="false">Sheet1!N10</f>
-        <v>3320</v>
-      </c>
-      <c r="E17" s="14" t="n">
-        <f aca="false">Sheet1!O10</f>
-        <v>3420</v>
-      </c>
-      <c r="F17" s="14" t="n">
-        <f aca="false">Sheet1!P10</f>
-        <v>3446</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="str">
-        <f aca="false">"Demand "&amp;Sheet1!$K$11</f>
-        <v>Demand 666502</v>
-      </c>
-      <c r="B18" s="14" t="n">
-        <f aca="false">Sheet1!L11</f>
-        <v>1800</v>
-      </c>
-      <c r="C18" s="14" t="n">
-        <f aca="false">Sheet1!M11</f>
-        <v>1950</v>
-      </c>
-      <c r="D18" s="14" t="n">
-        <f aca="false">Sheet1!N11</f>
-        <v>2050</v>
-      </c>
-      <c r="E18" s="14" t="n">
-        <f aca="false">Sheet1!O11</f>
-        <v>2075</v>
-      </c>
-      <c r="F18" s="14" t="n">
-        <f aca="false">Sheet1!P11</f>
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="str">
-        <f aca="false">"Demand "&amp;Sheet1!$K$12</f>
-        <v>Demand 666506</v>
-      </c>
-      <c r="B19" s="14" t="n">
-        <f aca="false">Sheet1!L12</f>
-        <v>735</v>
-      </c>
-      <c r="C19" s="14" t="n">
-        <f aca="false">Sheet1!M12</f>
-        <v>760</v>
-      </c>
-      <c r="D19" s="14" t="n">
-        <f aca="false">Sheet1!N12</f>
-        <v>805</v>
-      </c>
-      <c r="E19" s="14" t="n">
-        <f aca="false">Sheet1!O12</f>
-        <v>855</v>
-      </c>
-      <c r="F19" s="14" t="n">
-        <f aca="false">Sheet1!P12</f>
-        <v>888</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="str">
-        <f aca="false">"Demand "&amp;Sheet1!$K$13</f>
-        <v>Demand 666541</v>
-      </c>
-      <c r="B20" s="14" t="n">
-        <f aca="false">Sheet1!L13</f>
-        <v>1800</v>
-      </c>
-      <c r="C20" s="14" t="n">
-        <f aca="false">Sheet1!M13</f>
-        <v>1950</v>
-      </c>
-      <c r="D20" s="14" t="n">
-        <f aca="false">Sheet1!N13</f>
-        <v>2050</v>
-      </c>
-      <c r="E20" s="14" t="n">
-        <f aca="false">Sheet1!O13</f>
-        <v>2075</v>
-      </c>
-      <c r="F20" s="14" t="n">
-        <f aca="false">Sheet1!P13</f>
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="15" t="n">
-        <f aca="false">SUM(B17:B20)</f>
-        <v>7305</v>
-      </c>
-      <c r="C21" s="15" t="n">
-        <f aca="false">SUM(C17:C20)</f>
-        <v>7810</v>
-      </c>
-      <c r="D21" s="15" t="n">
-        <f aca="false">SUM(D17:D20)</f>
-        <v>8225</v>
-      </c>
-      <c r="E21" s="15" t="n">
-        <f aca="false">SUM(E17:E20)</f>
-        <v>8425</v>
-      </c>
-      <c r="F21" s="15" t="n">
-        <f aca="false">SUM(F17:F20)</f>
-        <v>8434</v>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B66" s="15" t="str">
+        <f aca="false">"Demand (tissue units): "&amp;'Chart Data'!B4&amp;" "&amp;TEXT('Chart Data'!B21,"#,##0")&amp;"  -  "&amp;'Chart Data'!C4&amp;" "&amp;TEXT('Chart Data'!C21,"#,##0")&amp;"  -  "&amp;'Chart Data'!D4&amp;" "&amp;TEXT('Chart Data'!D21,"#,##0")&amp;"  -  "&amp;'Chart Data'!E4&amp;" "&amp;TEXT('Chart Data'!E21,"#,##0")&amp;"  -  "&amp;'Chart Data'!F4&amp;" "&amp;TEXT('Chart Data'!F21,"#,##0")</f>
+        <v>Demand (tissue units): Q4'26 7,305  -  Q1'27 7,810  -  Q2'27 8,225  -  Q3'27 8,425  -  Q4'27 8,434</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B67" s="15" t="str">
+        <f aca="false">"Coverage (net harvested / demand): "&amp;TEXT('Chart Data'!B14/'Chart Data'!B21,"0.0")&amp;"x  -  "&amp;TEXT('Chart Data'!B14/'Chart Data'!C21,"0.0")&amp;"x  -  "&amp;TEXT('Chart Data'!B14/'Chart Data'!D21,"0.0")&amp;"x  -  "&amp;TEXT('Chart Data'!B14/'Chart Data'!E21,"0.0")&amp;"x  -  "&amp;TEXT('Chart Data'!B14/'Chart Data'!F21,"0.0")&amp;"x"</f>
+        <v>Coverage (net harvested / demand): 3.0x  -  2.8x  -  2.7x  -  2.6x  -  2.6x</v>
       </c>
     </row>
   </sheetData>
@@ -2269,4 +5134,1416 @@
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF1BAF7A"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B1:L47"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="29" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="30" t="n">
+        <f aca="false">'Chart Data'!B15</f>
+        <v>41990</v>
+      </c>
+      <c r="D5" s="30" t="n">
+        <f aca="false">'Chart Data'!B9</f>
+        <v>31732.9759753593</v>
+      </c>
+      <c r="F5" s="30" t="n">
+        <f aca="false">'Chart Data'!B14</f>
+        <v>21890.5406138028</v>
+      </c>
+      <c r="H5" s="30" t="n">
+        <f aca="false">MAX('Chart Data'!B21:F21)</f>
+        <v>8434</v>
+      </c>
+      <c r="J5" s="31" t="n">
+        <f aca="false">'Chart Data'!B14/MAX('Chart Data'!B21:F21)</f>
+        <v>2.59551109957349</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="15" t="str">
+        <f aca="false">"pass spec: "&amp;TEXT('Chart Data'!B9/'Chart Data'!B15,"0%")&amp;" of gross"</f>
+        <v>pass spec: 76% of gross</v>
+      </c>
+      <c r="F6" s="15" t="str">
+        <f aca="false">TEXT('Chart Data'!B14/'Chart Data'!B9,"0%")&amp;" of spec survive harvest"</f>
+        <v>69% of spec survive harvest</v>
+      </c>
+      <c r="H6" s="15" t="str">
+        <f aca="false">'Chart Data'!F4&amp;", +"&amp;TEXT(MAX('Chart Data'!B21:F21)/'Chart Data'!B21-1,"0%")&amp;" vs "&amp;'Chart Data'!B4</f>
+        <v>Q4'27, +15% vs Q4'26</v>
+      </c>
+      <c r="J6" s="32" t="str">
+        <f aca="false">TEXT('Chart Data'!B14/'Chart Data'!B21,"0.0")&amp;"x at "&amp;'Chart Data'!B4</f>
+        <v>3.0x at Q4'26</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="33" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="C34" s="35"/>
+      <c r="D34" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E34" s="35"/>
+      <c r="F34" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="G34" s="35"/>
+      <c r="H34" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="I34" s="35"/>
+      <c r="J34" s="36" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="37" t="str">
+        <f aca="false">Sheet1!$D$16</f>
+        <v>Martins</v>
+      </c>
+      <c r="D35" s="20" t="n">
+        <f aca="false">'Chart Data'!B22</f>
+        <v>32500</v>
+      </c>
+      <c r="F35" s="20" t="n">
+        <f aca="false">'Chart Data'!B5</f>
+        <v>24963.6036960986</v>
+      </c>
+      <c r="H35" s="20" t="n">
+        <f aca="false">'Chart Data'!B10</f>
+        <v>17220.7857529863</v>
+      </c>
+      <c r="J35" s="38" t="n">
+        <f aca="false">'Chart Data'!B10/'Chart Data'!B14</f>
+        <v>0.786677042691578</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="39" t="str">
+        <f aca="false">Sheet1!$D$17</f>
+        <v>Nahunta</v>
+      </c>
+      <c r="D36" s="20" t="n">
+        <f aca="false">'Chart Data'!B23</f>
+        <v>2340</v>
+      </c>
+      <c r="F36" s="20" t="n">
+        <f aca="false">'Chart Data'!B6</f>
+        <v>1797.3794661191</v>
+      </c>
+      <c r="H36" s="20" t="n">
+        <f aca="false">'Chart Data'!B11</f>
+        <v>1239.89657421501</v>
+      </c>
+      <c r="J36" s="38" t="n">
+        <f aca="false">'Chart Data'!B11/'Chart Data'!B14</f>
+        <v>0.0566407470737936</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="40" t="str">
+        <f aca="false">Sheet1!$D$18</f>
+        <v>Customs</v>
+      </c>
+      <c r="D37" s="20" t="n">
+        <f aca="false">'Chart Data'!B24</f>
+        <v>1950</v>
+      </c>
+      <c r="F37" s="20" t="n">
+        <f aca="false">'Chart Data'!B7</f>
+        <v>1497.81622176591</v>
+      </c>
+      <c r="H37" s="20" t="n">
+        <f aca="false">'Chart Data'!B12</f>
+        <v>1033.24714517918</v>
+      </c>
+      <c r="J37" s="38" t="n">
+        <f aca="false">'Chart Data'!B12/'Chart Data'!B14</f>
+        <v>0.0472006225614947</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="41" t="str">
+        <f aca="false">Sheet1!$D$19</f>
+        <v>Parks</v>
+      </c>
+      <c r="D38" s="20" t="n">
+        <f aca="false">'Chart Data'!B25</f>
+        <v>5200</v>
+      </c>
+      <c r="F38" s="20" t="n">
+        <f aca="false">'Chart Data'!B8</f>
+        <v>3474.17659137577</v>
+      </c>
+      <c r="H38" s="20" t="n">
+        <f aca="false">'Chart Data'!B13</f>
+        <v>2396.61114142236</v>
+      </c>
+      <c r="J38" s="38" t="n">
+        <f aca="false">'Chart Data'!B13/'Chart Data'!B14</f>
+        <v>0.109481587673134</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="C39" s="43"/>
+      <c r="D39" s="44" t="n">
+        <f aca="false">'Chart Data'!B15</f>
+        <v>41990</v>
+      </c>
+      <c r="E39" s="43"/>
+      <c r="F39" s="44" t="n">
+        <f aca="false">'Chart Data'!B9</f>
+        <v>31732.9759753593</v>
+      </c>
+      <c r="G39" s="43"/>
+      <c r="H39" s="44" t="n">
+        <f aca="false">'Chart Data'!B14</f>
+        <v>21890.5406138028</v>
+      </c>
+      <c r="I39" s="43"/>
+      <c r="J39" s="45" t="n">
+        <f aca="false">SUM(J35:J38)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="33" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="35"/>
+      <c r="C43" s="35"/>
+      <c r="D43" s="36" t="str">
+        <f aca="false">'Chart Data'!B4</f>
+        <v>Q4'26</v>
+      </c>
+      <c r="E43" s="35"/>
+      <c r="F43" s="36" t="str">
+        <f aca="false">'Chart Data'!C4</f>
+        <v>Q1'27</v>
+      </c>
+      <c r="G43" s="35"/>
+      <c r="H43" s="36" t="str">
+        <f aca="false">'Chart Data'!D4</f>
+        <v>Q2'27</v>
+      </c>
+      <c r="I43" s="35"/>
+      <c r="J43" s="36" t="str">
+        <f aca="false">'Chart Data'!E4</f>
+        <v>Q3'27</v>
+      </c>
+      <c r="K43" s="35"/>
+      <c r="L43" s="36" t="str">
+        <f aca="false">'Chart Data'!F4</f>
+        <v>Q4'27</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="D44" s="20" t="n">
+        <f aca="false">'Chart Data'!B21</f>
+        <v>7305</v>
+      </c>
+      <c r="F44" s="20" t="n">
+        <f aca="false">'Chart Data'!C21</f>
+        <v>7810</v>
+      </c>
+      <c r="H44" s="20" t="n">
+        <f aca="false">'Chart Data'!D21</f>
+        <v>8225</v>
+      </c>
+      <c r="J44" s="20" t="n">
+        <f aca="false">'Chart Data'!E21</f>
+        <v>8425</v>
+      </c>
+      <c r="L44" s="20" t="n">
+        <f aca="false">'Chart Data'!F21</f>
+        <v>8434</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D45" s="46" t="n">
+        <f aca="false">'Chart Data'!B14/'Chart Data'!B21</f>
+        <v>2.99665169251236</v>
+      </c>
+      <c r="F45" s="46" t="n">
+        <f aca="false">'Chart Data'!B14/'Chart Data'!C21</f>
+        <v>2.80288612212584</v>
+      </c>
+      <c r="H45" s="46" t="n">
+        <f aca="false">'Chart Data'!B14/'Chart Data'!D21</f>
+        <v>2.66146390441372</v>
+      </c>
+      <c r="J45" s="46" t="n">
+        <f aca="false">'Chart Data'!B14/'Chart Data'!E21</f>
+        <v>2.59828375238016</v>
+      </c>
+      <c r="L45" s="46" t="n">
+        <f aca="false">'Chart Data'!B14/'Chart Data'!F21</f>
+        <v>2.59551109957349</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="47" t="str">
+        <f aca="false">"Demand counted at 1 tissue unit = 1 pig equivalent; coverage = net harvested / demand. Net harvested = spec-passed x "&amp;TEXT('Chart Data'!B14/'Chart Data'!B9,"0%")&amp;" harvest yield."</f>
+        <v>Demand counted at 1 tissue unit = 1 pig equivalent; coverage = net harvested / demand. Net harvested = spec-passed x 69% harvest yield.</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FFEDA100"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B1:O38"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="12" style="0" width="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="11" t="str">
+        <f aca="false">"Pigs per quarter; supply flat, demand rising "&amp;TEXT('Chart Data'!B21,"#,##0")&amp;" to "&amp;TEXT('Chart Data'!F21,"#,##0")&amp;"."</f>
+        <v>Pigs per quarter; supply flat, demand rising 7,305 to 8,434.</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="12" t="n">
+        <f aca="false">'Chart Data'!B14/MAX('Chart Data'!B21:F21)</f>
+        <v>2.59551109957349</v>
+      </c>
+      <c r="E5" s="48" t="n">
+        <f aca="false">'Chart Data'!B14</f>
+        <v>21890.5406138028</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <f aca="false">'Chart Data'!B14/'Chart Data'!B15</f>
+        <v>0.521327473536624</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <f aca="false">'Chart Data'!B10/'Chart Data'!B14</f>
+        <v>0.786677042691578</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="15" t="str">
+        <f aca="false">TEXT('Chart Data'!B14-MAX('Chart Data'!B21:F21),"#,##0")&amp;" pigs/qtr headroom at peak"</f>
+        <v>13,457 pigs/qtr headroom at peak</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="H6" s="15" t="str">
+        <f aca="false">"spec "&amp;TEXT('Chart Data'!B9/'Chart Data'!B15,"0%")&amp;" x harvest "&amp;TEXT('Chart Data'!B14/'Chart Data'!B9,"0%")</f>
+        <v>spec 76% x harvest 69%</v>
+      </c>
+      <c r="K6" s="15" t="str">
+        <f aca="false">TEXT('Chart Data'!B10,"#,##0")&amp;" of "&amp;TEXT('Chart Data'!B14,"#,##0")</f>
+        <v>17,221 of 21,891</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="J28" s="33" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="D29" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E29" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="J29" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="K29" s="36" t="str">
+        <f aca="false">'Chart Data'!B4</f>
+        <v>Q4'26</v>
+      </c>
+      <c r="L29" s="36" t="str">
+        <f aca="false">'Chart Data'!C4</f>
+        <v>Q1'27</v>
+      </c>
+      <c r="M29" s="36" t="str">
+        <f aca="false">'Chart Data'!D4</f>
+        <v>Q2'27</v>
+      </c>
+      <c r="N29" s="36" t="str">
+        <f aca="false">'Chart Data'!E4</f>
+        <v>Q3'27</v>
+      </c>
+      <c r="O29" s="36" t="str">
+        <f aca="false">'Chart Data'!F4</f>
+        <v>Q4'27</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="19" t="str">
+        <f aca="false">Sheet1!$D$16</f>
+        <v>Martins</v>
+      </c>
+      <c r="C30" s="20" t="n">
+        <f aca="false">'Chart Data'!B22</f>
+        <v>32500</v>
+      </c>
+      <c r="D30" s="20" t="n">
+        <f aca="false">'Chart Data'!B5</f>
+        <v>24963.6036960986</v>
+      </c>
+      <c r="E30" s="20" t="n">
+        <f aca="false">'Chart Data'!B10</f>
+        <v>17220.7857529863</v>
+      </c>
+      <c r="J30" s="19" t="n">
+        <f aca="false">Sheet1!$K$10</f>
+        <v>666501</v>
+      </c>
+      <c r="K30" s="20" t="n">
+        <f aca="false">'Chart Data'!B17</f>
+        <v>2970</v>
+      </c>
+      <c r="L30" s="20" t="n">
+        <f aca="false">'Chart Data'!C17</f>
+        <v>3150</v>
+      </c>
+      <c r="M30" s="20" t="n">
+        <f aca="false">'Chart Data'!D17</f>
+        <v>3320</v>
+      </c>
+      <c r="N30" s="20" t="n">
+        <f aca="false">'Chart Data'!E17</f>
+        <v>3420</v>
+      </c>
+      <c r="O30" s="20" t="n">
+        <f aca="false">'Chart Data'!F17</f>
+        <v>3446</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="19" t="str">
+        <f aca="false">Sheet1!$D$17</f>
+        <v>Nahunta</v>
+      </c>
+      <c r="C31" s="20" t="n">
+        <f aca="false">'Chart Data'!B23</f>
+        <v>2340</v>
+      </c>
+      <c r="D31" s="20" t="n">
+        <f aca="false">'Chart Data'!B6</f>
+        <v>1797.3794661191</v>
+      </c>
+      <c r="E31" s="20" t="n">
+        <f aca="false">'Chart Data'!B11</f>
+        <v>1239.89657421501</v>
+      </c>
+      <c r="J31" s="19" t="n">
+        <f aca="false">Sheet1!$K$11</f>
+        <v>666502</v>
+      </c>
+      <c r="K31" s="20" t="n">
+        <f aca="false">'Chart Data'!B18</f>
+        <v>1800</v>
+      </c>
+      <c r="L31" s="20" t="n">
+        <f aca="false">'Chart Data'!C18</f>
+        <v>1950</v>
+      </c>
+      <c r="M31" s="20" t="n">
+        <f aca="false">'Chart Data'!D18</f>
+        <v>2050</v>
+      </c>
+      <c r="N31" s="20" t="n">
+        <f aca="false">'Chart Data'!E18</f>
+        <v>2075</v>
+      </c>
+      <c r="O31" s="20" t="n">
+        <f aca="false">'Chart Data'!F18</f>
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="19" t="str">
+        <f aca="false">Sheet1!$D$18</f>
+        <v>Customs</v>
+      </c>
+      <c r="C32" s="20" t="n">
+        <f aca="false">'Chart Data'!B24</f>
+        <v>1950</v>
+      </c>
+      <c r="D32" s="20" t="n">
+        <f aca="false">'Chart Data'!B7</f>
+        <v>1497.81622176591</v>
+      </c>
+      <c r="E32" s="20" t="n">
+        <f aca="false">'Chart Data'!B12</f>
+        <v>1033.24714517918</v>
+      </c>
+      <c r="J32" s="19" t="n">
+        <f aca="false">Sheet1!$K$12</f>
+        <v>666506</v>
+      </c>
+      <c r="K32" s="20" t="n">
+        <f aca="false">'Chart Data'!B19</f>
+        <v>735</v>
+      </c>
+      <c r="L32" s="20" t="n">
+        <f aca="false">'Chart Data'!C19</f>
+        <v>760</v>
+      </c>
+      <c r="M32" s="20" t="n">
+        <f aca="false">'Chart Data'!D19</f>
+        <v>805</v>
+      </c>
+      <c r="N32" s="20" t="n">
+        <f aca="false">'Chart Data'!E19</f>
+        <v>855</v>
+      </c>
+      <c r="O32" s="20" t="n">
+        <f aca="false">'Chart Data'!F19</f>
+        <v>888</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="19" t="str">
+        <f aca="false">Sheet1!$D$19</f>
+        <v>Parks</v>
+      </c>
+      <c r="C33" s="20" t="n">
+        <f aca="false">'Chart Data'!B25</f>
+        <v>5200</v>
+      </c>
+      <c r="D33" s="20" t="n">
+        <f aca="false">'Chart Data'!B8</f>
+        <v>3474.17659137577</v>
+      </c>
+      <c r="E33" s="20" t="n">
+        <f aca="false">'Chart Data'!B13</f>
+        <v>2396.61114142236</v>
+      </c>
+      <c r="J33" s="19" t="n">
+        <f aca="false">Sheet1!$K$13</f>
+        <v>666541</v>
+      </c>
+      <c r="K33" s="20" t="n">
+        <f aca="false">'Chart Data'!B20</f>
+        <v>1800</v>
+      </c>
+      <c r="L33" s="20" t="n">
+        <f aca="false">'Chart Data'!C20</f>
+        <v>1950</v>
+      </c>
+      <c r="M33" s="20" t="n">
+        <f aca="false">'Chart Data'!D20</f>
+        <v>2050</v>
+      </c>
+      <c r="N33" s="20" t="n">
+        <f aca="false">'Chart Data'!E20</f>
+        <v>2075</v>
+      </c>
+      <c r="O33" s="20" t="n">
+        <f aca="false">'Chart Data'!F20</f>
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" s="44" t="n">
+        <f aca="false">'Chart Data'!B15</f>
+        <v>41990</v>
+      </c>
+      <c r="D34" s="44" t="n">
+        <f aca="false">'Chart Data'!B9</f>
+        <v>31732.9759753593</v>
+      </c>
+      <c r="E34" s="44" t="n">
+        <f aca="false">'Chart Data'!B14</f>
+        <v>21890.5406138028</v>
+      </c>
+      <c r="J34" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="K34" s="44" t="n">
+        <f aca="false">'Chart Data'!B21</f>
+        <v>7305</v>
+      </c>
+      <c r="L34" s="44" t="n">
+        <f aca="false">'Chart Data'!C21</f>
+        <v>7810</v>
+      </c>
+      <c r="M34" s="44" t="n">
+        <f aca="false">'Chart Data'!D21</f>
+        <v>8225</v>
+      </c>
+      <c r="N34" s="44" t="n">
+        <f aca="false">'Chart Data'!E21</f>
+        <v>8425</v>
+      </c>
+      <c r="O34" s="44" t="n">
+        <f aca="false">'Chart Data'!F21</f>
+        <v>8434</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="47" t="str">
+        <f aca="false">"Yields: "&amp;TEXT('Chart Data'!B15,"#,##0")&amp;" gross x "&amp;TEXT('Chart Data'!B9/'Chart Data'!B15,"0%")&amp;" spec = "&amp;TEXT('Chart Data'!B9,"#,##0")&amp;"; x "&amp;TEXT('Chart Data'!B14/'Chart Data'!B9,"0%")&amp;" harvest = "&amp;TEXT('Chart Data'!B14,"#,##0")&amp;" available per quarter."</f>
+        <v>Yields: 41,990 gross x 76% spec = 31,733; x 69% harvest = 21,891 available per quarter.</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="49" t="s">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF808080"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="9" style="0" width="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="50" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H3" s="52" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="54" t="str">
+        <f aca="false">Sheet1!L9</f>
+        <v>Q4'26</v>
+      </c>
+      <c r="C4" s="54" t="str">
+        <f aca="false">Sheet1!M9</f>
+        <v>Q1'27</v>
+      </c>
+      <c r="D4" s="54" t="str">
+        <f aca="false">Sheet1!N9</f>
+        <v>Q2'27</v>
+      </c>
+      <c r="E4" s="54" t="str">
+        <f aca="false">Sheet1!O9</f>
+        <v>Q3'27</v>
+      </c>
+      <c r="F4" s="54" t="str">
+        <f aca="false">Sheet1!P9</f>
+        <v>Q4'27</v>
+      </c>
+      <c r="H4" s="55"/>
+      <c r="I4" s="56" t="str">
+        <f aca="false">"Gross kill"&amp;CHAR(10)&amp;TEXT(B15,"#,##0")</f>
+        <v>Gross kill
+41,990</v>
+      </c>
+      <c r="J4" s="56" t="str">
+        <f aca="false">"After spec yield"&amp;CHAR(10)&amp;TEXT(B9,"#,##0")&amp;"  (-"&amp;TEXT(1-B9/B15,"0%")&amp;")"</f>
+        <v>After spec yield
+31,733  (-24%)</v>
+      </c>
+      <c r="K4" s="56" t="str">
+        <f aca="false">"After harvest yield"&amp;CHAR(10)&amp;TEXT(B14,"#,##0")&amp;"  (-"&amp;TEXT(1-B14/B9,"0%")&amp;")"</f>
+        <v>After harvest yield
+21,891  (-31%)</v>
+      </c>
+      <c r="L4" s="56" t="str">
+        <f aca="false">"Peak demand Q4'27"&amp;CHAR(10)&amp;TEXT(F21,"#,##0")</f>
+        <v>Peak demand Q4'27
+8,434</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="57" t="str">
+        <f aca="false">Sheet1!$D$16&amp;" (net, spec yield)"</f>
+        <v>Martins (net, spec yield)</v>
+      </c>
+      <c r="B5" s="58" t="n">
+        <f aca="false">Sheet1!$H$16</f>
+        <v>24963.6036960986</v>
+      </c>
+      <c r="C5" s="58" t="n">
+        <f aca="false">Sheet1!$H$16</f>
+        <v>24963.6036960986</v>
+      </c>
+      <c r="D5" s="58" t="n">
+        <f aca="false">Sheet1!$H$16</f>
+        <v>24963.6036960986</v>
+      </c>
+      <c r="E5" s="58" t="n">
+        <f aca="false">Sheet1!$H$16</f>
+        <v>24963.6036960986</v>
+      </c>
+      <c r="F5" s="58" t="n">
+        <f aca="false">Sheet1!$H$16</f>
+        <v>24963.6036960986</v>
+      </c>
+      <c r="H5" s="57" t="str">
+        <f aca="false">Sheet1!$D$16</f>
+        <v>Martins</v>
+      </c>
+      <c r="I5" s="58" t="n">
+        <f aca="false">B22</f>
+        <v>32500</v>
+      </c>
+      <c r="J5" s="58" t="n">
+        <f aca="false">B5</f>
+        <v>24963.6036960986</v>
+      </c>
+      <c r="K5" s="58" t="n">
+        <f aca="false">B10</f>
+        <v>17220.7857529863</v>
+      </c>
+      <c r="L5" s="55"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="57" t="str">
+        <f aca="false">Sheet1!$D$17&amp;" (net, spec yield)"</f>
+        <v>Nahunta (net, spec yield)</v>
+      </c>
+      <c r="B6" s="58" t="n">
+        <f aca="false">Sheet1!$H$17</f>
+        <v>1797.3794661191</v>
+      </c>
+      <c r="C6" s="58" t="n">
+        <f aca="false">Sheet1!$H$17</f>
+        <v>1797.3794661191</v>
+      </c>
+      <c r="D6" s="58" t="n">
+        <f aca="false">Sheet1!$H$17</f>
+        <v>1797.3794661191</v>
+      </c>
+      <c r="E6" s="58" t="n">
+        <f aca="false">Sheet1!$H$17</f>
+        <v>1797.3794661191</v>
+      </c>
+      <c r="F6" s="58" t="n">
+        <f aca="false">Sheet1!$H$17</f>
+        <v>1797.3794661191</v>
+      </c>
+      <c r="H6" s="57" t="str">
+        <f aca="false">Sheet1!$D$17</f>
+        <v>Nahunta</v>
+      </c>
+      <c r="I6" s="58" t="n">
+        <f aca="false">B23</f>
+        <v>2340</v>
+      </c>
+      <c r="J6" s="58" t="n">
+        <f aca="false">B6</f>
+        <v>1797.3794661191</v>
+      </c>
+      <c r="K6" s="58" t="n">
+        <f aca="false">B11</f>
+        <v>1239.89657421501</v>
+      </c>
+      <c r="L6" s="55"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="57" t="str">
+        <f aca="false">Sheet1!$D$18&amp;" (net, spec yield)"</f>
+        <v>Customs (net, spec yield)</v>
+      </c>
+      <c r="B7" s="58" t="n">
+        <f aca="false">Sheet1!$H$18</f>
+        <v>1497.81622176591</v>
+      </c>
+      <c r="C7" s="58" t="n">
+        <f aca="false">Sheet1!$H$18</f>
+        <v>1497.81622176591</v>
+      </c>
+      <c r="D7" s="58" t="n">
+        <f aca="false">Sheet1!$H$18</f>
+        <v>1497.81622176591</v>
+      </c>
+      <c r="E7" s="58" t="n">
+        <f aca="false">Sheet1!$H$18</f>
+        <v>1497.81622176591</v>
+      </c>
+      <c r="F7" s="58" t="n">
+        <f aca="false">Sheet1!$H$18</f>
+        <v>1497.81622176591</v>
+      </c>
+      <c r="H7" s="57" t="str">
+        <f aca="false">Sheet1!$D$18</f>
+        <v>Customs</v>
+      </c>
+      <c r="I7" s="58" t="n">
+        <f aca="false">B24</f>
+        <v>1950</v>
+      </c>
+      <c r="J7" s="58" t="n">
+        <f aca="false">B7</f>
+        <v>1497.81622176591</v>
+      </c>
+      <c r="K7" s="58" t="n">
+        <f aca="false">B12</f>
+        <v>1033.24714517918</v>
+      </c>
+      <c r="L7" s="55"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="57" t="str">
+        <f aca="false">Sheet1!$D$19&amp;" (net, spec yield)"</f>
+        <v>Parks (net, spec yield)</v>
+      </c>
+      <c r="B8" s="58" t="n">
+        <f aca="false">Sheet1!$H$19</f>
+        <v>3474.17659137577</v>
+      </c>
+      <c r="C8" s="58" t="n">
+        <f aca="false">Sheet1!$H$19</f>
+        <v>3474.17659137577</v>
+      </c>
+      <c r="D8" s="58" t="n">
+        <f aca="false">Sheet1!$H$19</f>
+        <v>3474.17659137577</v>
+      </c>
+      <c r="E8" s="58" t="n">
+        <f aca="false">Sheet1!$H$19</f>
+        <v>3474.17659137577</v>
+      </c>
+      <c r="F8" s="58" t="n">
+        <f aca="false">Sheet1!$H$19</f>
+        <v>3474.17659137577</v>
+      </c>
+      <c r="H8" s="57" t="str">
+        <f aca="false">Sheet1!$D$19</f>
+        <v>Parks</v>
+      </c>
+      <c r="I8" s="58" t="n">
+        <f aca="false">B25</f>
+        <v>5200</v>
+      </c>
+      <c r="J8" s="58" t="n">
+        <f aca="false">B8</f>
+        <v>3474.17659137577</v>
+      </c>
+      <c r="K8" s="58" t="n">
+        <f aca="false">B13</f>
+        <v>2396.61114142236</v>
+      </c>
+      <c r="L8" s="55"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="59" t="n">
+        <f aca="false">SUM(B5:B8)</f>
+        <v>31732.9759753593</v>
+      </c>
+      <c r="C9" s="59" t="n">
+        <f aca="false">SUM(C5:C8)</f>
+        <v>31732.9759753593</v>
+      </c>
+      <c r="D9" s="59" t="n">
+        <f aca="false">SUM(D5:D8)</f>
+        <v>31732.9759753593</v>
+      </c>
+      <c r="E9" s="59" t="n">
+        <f aca="false">SUM(E5:E8)</f>
+        <v>31732.9759753593</v>
+      </c>
+      <c r="F9" s="59" t="n">
+        <f aca="false">SUM(F5:F8)</f>
+        <v>31732.9759753593</v>
+      </c>
+      <c r="H9" s="57" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" s="55"/>
+      <c r="J9" s="55"/>
+      <c r="K9" s="55"/>
+      <c r="L9" s="58" t="n">
+        <f aca="false">F21</f>
+        <v>8434</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="57" t="str">
+        <f aca="false">Sheet1!$D$16&amp;" (net harvested)"</f>
+        <v>Martins (net harvested)</v>
+      </c>
+      <c r="B10" s="58" t="n">
+        <f aca="false">Sheet1!$J$16</f>
+        <v>17220.7857529863</v>
+      </c>
+      <c r="C10" s="58" t="n">
+        <f aca="false">Sheet1!$J$16</f>
+        <v>17220.7857529863</v>
+      </c>
+      <c r="D10" s="58" t="n">
+        <f aca="false">Sheet1!$J$16</f>
+        <v>17220.7857529863</v>
+      </c>
+      <c r="E10" s="58" t="n">
+        <f aca="false">Sheet1!$J$16</f>
+        <v>17220.7857529863</v>
+      </c>
+      <c r="F10" s="58" t="n">
+        <f aca="false">Sheet1!$J$16</f>
+        <v>17220.7857529863</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="57" t="str">
+        <f aca="false">Sheet1!$D$17&amp;" (net harvested)"</f>
+        <v>Nahunta (net harvested)</v>
+      </c>
+      <c r="B11" s="58" t="n">
+        <f aca="false">Sheet1!$J$17</f>
+        <v>1239.89657421501</v>
+      </c>
+      <c r="C11" s="58" t="n">
+        <f aca="false">Sheet1!$J$17</f>
+        <v>1239.89657421501</v>
+      </c>
+      <c r="D11" s="58" t="n">
+        <f aca="false">Sheet1!$J$17</f>
+        <v>1239.89657421501</v>
+      </c>
+      <c r="E11" s="58" t="n">
+        <f aca="false">Sheet1!$J$17</f>
+        <v>1239.89657421501</v>
+      </c>
+      <c r="F11" s="58" t="n">
+        <f aca="false">Sheet1!$J$17</f>
+        <v>1239.89657421501</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="57" t="str">
+        <f aca="false">Sheet1!$D$18&amp;" (net harvested)"</f>
+        <v>Customs (net harvested)</v>
+      </c>
+      <c r="B12" s="58" t="n">
+        <f aca="false">Sheet1!$J$18</f>
+        <v>1033.24714517918</v>
+      </c>
+      <c r="C12" s="58" t="n">
+        <f aca="false">Sheet1!$J$18</f>
+        <v>1033.24714517918</v>
+      </c>
+      <c r="D12" s="58" t="n">
+        <f aca="false">Sheet1!$J$18</f>
+        <v>1033.24714517918</v>
+      </c>
+      <c r="E12" s="58" t="n">
+        <f aca="false">Sheet1!$J$18</f>
+        <v>1033.24714517918</v>
+      </c>
+      <c r="F12" s="58" t="n">
+        <f aca="false">Sheet1!$J$18</f>
+        <v>1033.24714517918</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="57" t="str">
+        <f aca="false">Sheet1!$D$19&amp;" (net harvested)"</f>
+        <v>Parks (net harvested)</v>
+      </c>
+      <c r="B13" s="58" t="n">
+        <f aca="false">Sheet1!$J$19</f>
+        <v>2396.61114142236</v>
+      </c>
+      <c r="C13" s="58" t="n">
+        <f aca="false">Sheet1!$J$19</f>
+        <v>2396.61114142236</v>
+      </c>
+      <c r="D13" s="58" t="n">
+        <f aca="false">Sheet1!$J$19</f>
+        <v>2396.61114142236</v>
+      </c>
+      <c r="E13" s="58" t="n">
+        <f aca="false">Sheet1!$J$19</f>
+        <v>2396.61114142236</v>
+      </c>
+      <c r="F13" s="58" t="n">
+        <f aca="false">Sheet1!$J$19</f>
+        <v>2396.61114142236</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="53" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" s="59" t="n">
+        <f aca="false">SUM(B10:B13)</f>
+        <v>21890.5406138028</v>
+      </c>
+      <c r="C14" s="59" t="n">
+        <f aca="false">SUM(C10:C13)</f>
+        <v>21890.5406138028</v>
+      </c>
+      <c r="D14" s="59" t="n">
+        <f aca="false">SUM(D10:D13)</f>
+        <v>21890.5406138028</v>
+      </c>
+      <c r="E14" s="59" t="n">
+        <f aca="false">SUM(E10:E13)</f>
+        <v>21890.5406138028</v>
+      </c>
+      <c r="F14" s="59" t="n">
+        <f aca="false">SUM(F10:F13)</f>
+        <v>21890.5406138028</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="53" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" s="59" t="n">
+        <f aca="false">SUM(Sheet1!$F$16:$F$19)</f>
+        <v>41990</v>
+      </c>
+      <c r="C15" s="59" t="n">
+        <f aca="false">SUM(Sheet1!$F$16:$F$19)</f>
+        <v>41990</v>
+      </c>
+      <c r="D15" s="59" t="n">
+        <f aca="false">SUM(Sheet1!$F$16:$F$19)</f>
+        <v>41990</v>
+      </c>
+      <c r="E15" s="59" t="n">
+        <f aca="false">SUM(Sheet1!$F$16:$F$19)</f>
+        <v>41990</v>
+      </c>
+      <c r="F15" s="59" t="n">
+        <f aca="false">SUM(Sheet1!$F$16:$F$19)</f>
+        <v>41990</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="57" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" s="58" t="n">
+        <f aca="false">B15-B9</f>
+        <v>10257.0240246407</v>
+      </c>
+      <c r="C16" s="58" t="n">
+        <f aca="false">C15-C9</f>
+        <v>10257.0240246407</v>
+      </c>
+      <c r="D16" s="58" t="n">
+        <f aca="false">D15-D9</f>
+        <v>10257.0240246407</v>
+      </c>
+      <c r="E16" s="58" t="n">
+        <f aca="false">E15-E9</f>
+        <v>10257.0240246407</v>
+      </c>
+      <c r="F16" s="58" t="n">
+        <f aca="false">F15-F9</f>
+        <v>10257.0240246407</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="57" t="str">
+        <f aca="false">"Demand "&amp;Sheet1!$K$10</f>
+        <v>Demand 666501</v>
+      </c>
+      <c r="B17" s="58" t="n">
+        <f aca="false">Sheet1!L10</f>
+        <v>2970</v>
+      </c>
+      <c r="C17" s="58" t="n">
+        <f aca="false">Sheet1!M10</f>
+        <v>3150</v>
+      </c>
+      <c r="D17" s="58" t="n">
+        <f aca="false">Sheet1!N10</f>
+        <v>3320</v>
+      </c>
+      <c r="E17" s="58" t="n">
+        <f aca="false">Sheet1!O10</f>
+        <v>3420</v>
+      </c>
+      <c r="F17" s="58" t="n">
+        <f aca="false">Sheet1!P10</f>
+        <v>3446</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="57" t="str">
+        <f aca="false">"Demand "&amp;Sheet1!$K$11</f>
+        <v>Demand 666502</v>
+      </c>
+      <c r="B18" s="58" t="n">
+        <f aca="false">Sheet1!L11</f>
+        <v>1800</v>
+      </c>
+      <c r="C18" s="58" t="n">
+        <f aca="false">Sheet1!M11</f>
+        <v>1950</v>
+      </c>
+      <c r="D18" s="58" t="n">
+        <f aca="false">Sheet1!N11</f>
+        <v>2050</v>
+      </c>
+      <c r="E18" s="58" t="n">
+        <f aca="false">Sheet1!O11</f>
+        <v>2075</v>
+      </c>
+      <c r="F18" s="58" t="n">
+        <f aca="false">Sheet1!P11</f>
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="57" t="str">
+        <f aca="false">"Demand "&amp;Sheet1!$K$12</f>
+        <v>Demand 666506</v>
+      </c>
+      <c r="B19" s="58" t="n">
+        <f aca="false">Sheet1!L12</f>
+        <v>735</v>
+      </c>
+      <c r="C19" s="58" t="n">
+        <f aca="false">Sheet1!M12</f>
+        <v>760</v>
+      </c>
+      <c r="D19" s="58" t="n">
+        <f aca="false">Sheet1!N12</f>
+        <v>805</v>
+      </c>
+      <c r="E19" s="58" t="n">
+        <f aca="false">Sheet1!O12</f>
+        <v>855</v>
+      </c>
+      <c r="F19" s="58" t="n">
+        <f aca="false">Sheet1!P12</f>
+        <v>888</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="57" t="str">
+        <f aca="false">"Demand "&amp;Sheet1!$K$13</f>
+        <v>Demand 666541</v>
+      </c>
+      <c r="B20" s="58" t="n">
+        <f aca="false">Sheet1!L13</f>
+        <v>1800</v>
+      </c>
+      <c r="C20" s="58" t="n">
+        <f aca="false">Sheet1!M13</f>
+        <v>1950</v>
+      </c>
+      <c r="D20" s="58" t="n">
+        <f aca="false">Sheet1!N13</f>
+        <v>2050</v>
+      </c>
+      <c r="E20" s="58" t="n">
+        <f aca="false">Sheet1!O13</f>
+        <v>2075</v>
+      </c>
+      <c r="F20" s="58" t="n">
+        <f aca="false">Sheet1!P13</f>
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="53" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="59" t="n">
+        <f aca="false">SUM(B17:B20)</f>
+        <v>7305</v>
+      </c>
+      <c r="C21" s="59" t="n">
+        <f aca="false">SUM(C17:C20)</f>
+        <v>7810</v>
+      </c>
+      <c r="D21" s="59" t="n">
+        <f aca="false">SUM(D17:D20)</f>
+        <v>8225</v>
+      </c>
+      <c r="E21" s="59" t="n">
+        <f aca="false">SUM(E17:E20)</f>
+        <v>8425</v>
+      </c>
+      <c r="F21" s="59" t="n">
+        <f aca="false">SUM(F17:F20)</f>
+        <v>8434</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="57" t="str">
+        <f aca="false">Sheet1!$D$16&amp;" (gross kill)"</f>
+        <v>Martins (gross kill)</v>
+      </c>
+      <c r="B22" s="58" t="n">
+        <f aca="false">Sheet1!$F$16</f>
+        <v>32500</v>
+      </c>
+      <c r="C22" s="58" t="n">
+        <f aca="false">Sheet1!$F$16</f>
+        <v>32500</v>
+      </c>
+      <c r="D22" s="58" t="n">
+        <f aca="false">Sheet1!$F$16</f>
+        <v>32500</v>
+      </c>
+      <c r="E22" s="58" t="n">
+        <f aca="false">Sheet1!$F$16</f>
+        <v>32500</v>
+      </c>
+      <c r="F22" s="58" t="n">
+        <f aca="false">Sheet1!$F$16</f>
+        <v>32500</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="57" t="str">
+        <f aca="false">Sheet1!$D$17&amp;" (gross kill)"</f>
+        <v>Nahunta (gross kill)</v>
+      </c>
+      <c r="B23" s="58" t="n">
+        <f aca="false">Sheet1!$F$17</f>
+        <v>2340</v>
+      </c>
+      <c r="C23" s="58" t="n">
+        <f aca="false">Sheet1!$F$17</f>
+        <v>2340</v>
+      </c>
+      <c r="D23" s="58" t="n">
+        <f aca="false">Sheet1!$F$17</f>
+        <v>2340</v>
+      </c>
+      <c r="E23" s="58" t="n">
+        <f aca="false">Sheet1!$F$17</f>
+        <v>2340</v>
+      </c>
+      <c r="F23" s="58" t="n">
+        <f aca="false">Sheet1!$F$17</f>
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="57" t="str">
+        <f aca="false">Sheet1!$D$18&amp;" (gross kill)"</f>
+        <v>Customs (gross kill)</v>
+      </c>
+      <c r="B24" s="58" t="n">
+        <f aca="false">Sheet1!$F$18</f>
+        <v>1950</v>
+      </c>
+      <c r="C24" s="58" t="n">
+        <f aca="false">Sheet1!$F$18</f>
+        <v>1950</v>
+      </c>
+      <c r="D24" s="58" t="n">
+        <f aca="false">Sheet1!$F$18</f>
+        <v>1950</v>
+      </c>
+      <c r="E24" s="58" t="n">
+        <f aca="false">Sheet1!$F$18</f>
+        <v>1950</v>
+      </c>
+      <c r="F24" s="58" t="n">
+        <f aca="false">Sheet1!$F$18</f>
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="57" t="str">
+        <f aca="false">Sheet1!$D$19&amp;" (gross kill)"</f>
+        <v>Parks (gross kill)</v>
+      </c>
+      <c r="B25" s="58" t="n">
+        <f aca="false">Sheet1!$F$19</f>
+        <v>5200</v>
+      </c>
+      <c r="C25" s="58" t="n">
+        <f aca="false">Sheet1!$F$19</f>
+        <v>5200</v>
+      </c>
+      <c r="D25" s="58" t="n">
+        <f aca="false">Sheet1!$F$19</f>
+        <v>5200</v>
+      </c>
+      <c r="E25" s="58" t="n">
+        <f aca="false">Sheet1!$F$19</f>
+        <v>5200</v>
+      </c>
+      <c r="F25" s="58" t="n">
+        <f aca="false">Sheet1!$F$19</f>
+        <v>5200</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:L2"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/PVA second supplier initiative/Supplier_Capacity_Inputs.xlsx
+++ b/PVA second supplier initiative/Supplier_Capacity_Inputs.xlsx
@@ -373,6 +373,13 @@
       <family val="2"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF0B0B0B"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF595959"/>
       <name val="Aptos Narrow"/>
@@ -382,13 +389,6 @@
       <b val="true"/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="9"/>
-      <color rgb="FF0B0B0B"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
@@ -932,9 +932,9 @@
       <rgbColor rgb="FF800000"/>
       <rgbColor rgb="FF008300"/>
       <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF459428"/>
+      <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF7F7F7F"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFBFBFBF"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF889AAA"/>
@@ -963,7 +963,7 @@
       <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF2A78D6"/>
       <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF4EA72E"/>
+      <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFEDA100"/>
       <rgbColor rgb="FFEB6834"/>
@@ -1114,7 +1114,7 @@
           <dLbls>
             <dLbl>
               <idx val="0"/>
-              <numFmt formatCode="#,##0.0,&quot;K&quot;"/>
+              <numFmt formatCode="#,##0"/>
               <dLblPos val="ctr"/>
               <showLegendKey val="0"/>
               <showVal val="1"/>
@@ -1123,7 +1123,7 @@
               <showPercent val="0"/>
               <showBubbleSize val="0"/>
             </dLbl>
-            <numFmt formatCode="#,##0.0,&quot;K&quot;"/>
+            <numFmt formatCode="#,##0"/>
             <txPr>
               <a:bodyPr/>
               <a:p>
@@ -1231,7 +1231,7 @@
           <dLbls>
             <dLbl>
               <idx val="0"/>
-              <numFmt formatCode="#,##0.0,&quot;K&quot;"/>
+              <numFmt formatCode="#,##0"/>
               <dLblPos val="ctr"/>
               <showLegendKey val="0"/>
               <showVal val="1"/>
@@ -1240,7 +1240,7 @@
               <showPercent val="0"/>
               <showBubbleSize val="0"/>
             </dLbl>
-            <numFmt formatCode="#,##0.0,&quot;K&quot;"/>
+            <numFmt formatCode="#,##0"/>
             <txPr>
               <a:bodyPr/>
               <a:p>
@@ -1331,7 +1331,7 @@
           <dLbls>
             <dLbl>
               <idx val="4"/>
-              <numFmt formatCode="#,##0.0,&quot;K&quot;"/>
+              <numFmt formatCode="#,##0"/>
               <dLblPos val="t"/>
               <showLegendKey val="0"/>
               <showVal val="1"/>
@@ -1340,7 +1340,7 @@
               <showPercent val="0"/>
               <showBubbleSize val="0"/>
             </dLbl>
-            <numFmt formatCode="#,##0.0,&quot;K&quot;"/>
+            <numFmt formatCode="#,##0"/>
             <txPr>
               <a:bodyPr/>
               <a:p>
@@ -1377,8 +1377,131 @@
           </val>
           <smooth val="0"/>
         </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <v>Total (label)</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <numFmt formatCode="#,##0"/>
+            <txPr>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0">
+                    <a:solidFill>
+                      <a:srgbClr val="0B0B0B"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+                <a:endParaRPr sz="900" b="1" i="0">
+                  <a:solidFill>
+                    <a:srgbClr val="0B0B0B"/>
+                  </a:solidFill>
+                  <a:latin typeface="Aptos Narrow"/>
+                </a:endParaRPr>
+              </a:p>
+            </txPr>
+            <dLblPos val="t"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+            <showBubbleSize val="0"/>
+          </dLbls>
+          <val>
+            <numRef>
+              <f>'Chart Data'!$B$9:$F$9</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
         <axId val="10"/>
         <axId val="200"/>
+      </lineChart>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <v>Total (label)</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <numFmt formatCode="#,##0"/>
+            <txPr>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0">
+                    <a:solidFill>
+                      <a:srgbClr val="0B0B0B"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+                <a:endParaRPr sz="900" b="1" i="0">
+                  <a:solidFill>
+                    <a:srgbClr val="0B0B0B"/>
+                  </a:solidFill>
+                  <a:latin typeface="Aptos Narrow"/>
+                </a:endParaRPr>
+              </a:p>
+            </txPr>
+            <dLblPos val="t"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+            <showBubbleSize val="0"/>
+          </dLbls>
+          <val>
+            <numRef>
+              <f>'Chart Data'!$B$15:$F$15</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
       </lineChart>
       <catAx>
         <axId val="10"/>
@@ -1497,6 +1620,14 @@
       <legendPos val="b"/>
       <legendEntry>
         <idx val="0"/>
+        <delete val="1"/>
+      </legendEntry>
+      <legendEntry>
+        <idx val="6"/>
+        <delete val="1"/>
+      </legendEntry>
+      <legendEntry>
+        <idx val="7"/>
         <delete val="1"/>
       </legendEntry>
       <layout>
@@ -1704,7 +1835,7 @@
           <dLbls>
             <dLbl>
               <idx val="0"/>
-              <numFmt formatCode="#,##0.0,&quot;K&quot;"/>
+              <numFmt formatCode="#,##0"/>
               <dLblPos val="ctr"/>
               <showLegendKey val="0"/>
               <showVal val="1"/>
@@ -1713,7 +1844,7 @@
               <showPercent val="0"/>
               <showBubbleSize val="0"/>
             </dLbl>
-            <numFmt formatCode="#,##0.0,&quot;K&quot;"/>
+            <numFmt formatCode="#,##0"/>
             <txPr>
               <a:bodyPr/>
               <a:p>
@@ -1879,7 +2010,7 @@
           <dLbls>
             <dLbl>
               <idx val="4"/>
-              <numFmt formatCode="#,##0.0,&quot;K&quot;"/>
+              <numFmt formatCode="#,##0"/>
               <dLblPos val="t"/>
               <showLegendKey val="0"/>
               <showVal val="1"/>
@@ -1888,7 +2019,7 @@
               <showPercent val="0"/>
               <showBubbleSize val="0"/>
             </dLbl>
-            <numFmt formatCode="#,##0.0,&quot;K&quot;"/>
+            <numFmt formatCode="#,##0"/>
             <txPr>
               <a:bodyPr/>
               <a:p>
@@ -1925,8 +2056,131 @@
           </val>
           <smooth val="0"/>
         </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <v>Total (label)</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <numFmt formatCode="#,##0"/>
+            <txPr>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0">
+                    <a:solidFill>
+                      <a:srgbClr val="0B0B0B"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+                <a:endParaRPr sz="900" b="1" i="0">
+                  <a:solidFill>
+                    <a:srgbClr val="0B0B0B"/>
+                  </a:solidFill>
+                  <a:latin typeface="Aptos Narrow"/>
+                </a:endParaRPr>
+              </a:p>
+            </txPr>
+            <dLblPos val="t"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+            <showBubbleSize val="0"/>
+          </dLbls>
+          <val>
+            <numRef>
+              <f>'Chart Data'!$B$14:$F$14</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
         <axId val="10"/>
         <axId val="200"/>
+      </lineChart>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="8"/>
+          <order val="8"/>
+          <tx>
+            <v>Total (label)</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <numFmt formatCode="#,##0"/>
+            <txPr>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0">
+                    <a:solidFill>
+                      <a:srgbClr val="0B0B0B"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+                <a:endParaRPr sz="900" b="1" i="0">
+                  <a:solidFill>
+                    <a:srgbClr val="0B0B0B"/>
+                  </a:solidFill>
+                  <a:latin typeface="Aptos Narrow"/>
+                </a:endParaRPr>
+              </a:p>
+            </txPr>
+            <dLblPos val="t"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+            <showBubbleSize val="0"/>
+          </dLbls>
+          <val>
+            <numRef>
+              <f>'Chart Data'!$B$15:$F$15</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
       </lineChart>
       <catAx>
         <axId val="10"/>
@@ -2049,6 +2303,14 @@
       </legendEntry>
       <legendEntry>
         <idx val="1"/>
+        <delete val="1"/>
+      </legendEntry>
+      <legendEntry>
+        <idx val="7"/>
+        <delete val="1"/>
+      </legendEntry>
+      <legendEntry>
+        <idx val="8"/>
         <delete val="1"/>
       </legendEntry>
       <layout>
@@ -2454,8 +2716,131 @@
           </val>
           <smooth val="0"/>
         </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <v>Total (label)</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <numFmt formatCode="#,##0"/>
+            <txPr>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0">
+                    <a:solidFill>
+                      <a:srgbClr val="0B0B0B"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+                <a:endParaRPr sz="900" b="1" i="0">
+                  <a:solidFill>
+                    <a:srgbClr val="0B0B0B"/>
+                  </a:solidFill>
+                  <a:latin typeface="Aptos Narrow"/>
+                </a:endParaRPr>
+              </a:p>
+            </txPr>
+            <dLblPos val="t"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+            <showBubbleSize val="0"/>
+          </dLbls>
+          <val>
+            <numRef>
+              <f>'Chart Data'!$B$14:$F$14</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
         <axId val="10"/>
         <axId val="200"/>
+      </lineChart>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="8"/>
+          <order val="8"/>
+          <tx>
+            <v>Total (label)</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <numFmt formatCode="#,##0"/>
+            <txPr>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0">
+                    <a:solidFill>
+                      <a:srgbClr val="0B0B0B"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+                <a:endParaRPr sz="900" b="1" i="0">
+                  <a:solidFill>
+                    <a:srgbClr val="0B0B0B"/>
+                  </a:solidFill>
+                  <a:latin typeface="Aptos Narrow"/>
+                </a:endParaRPr>
+              </a:p>
+            </txPr>
+            <dLblPos val="t"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+            <showBubbleSize val="0"/>
+          </dLbls>
+          <val>
+            <numRef>
+              <f>'Chart Data'!$B$15:$F$15</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
       </lineChart>
       <catAx>
         <axId val="10"/>
@@ -2578,6 +2963,14 @@
       </legendEntry>
       <legendEntry>
         <idx val="1"/>
+        <delete val="1"/>
+      </legendEntry>
+      <legendEntry>
+        <idx val="7"/>
+        <delete val="1"/>
+      </legendEntry>
+      <legendEntry>
+        <idx val="8"/>
         <delete val="1"/>
       </legendEntry>
       <overlay val="0"/>
@@ -2954,6 +3347,65 @@
           </val>
           <smooth val="0"/>
         </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <v>Total (label)</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <numFmt formatCode="#,##0"/>
+            <txPr>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0">
+                    <a:solidFill>
+                      <a:srgbClr val="0B0B0B"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+                <a:endParaRPr sz="900" b="1" i="0">
+                  <a:solidFill>
+                    <a:srgbClr val="0B0B0B"/>
+                  </a:solidFill>
+                  <a:latin typeface="Aptos Narrow"/>
+                </a:endParaRPr>
+              </a:p>
+            </txPr>
+            <dLblPos val="t"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+            <showBubbleSize val="0"/>
+          </dLbls>
+          <val>
+            <numRef>
+              <f>'Chart Data'!$B$14:$F$14</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -3058,6 +3510,10 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <legendEntry>
+        <idx val="5"/>
+        <delete val="1"/>
+      </legendEntry>
       <overlay val="0"/>
       <txPr>
         <a:bodyPr/>

--- a/PVA second supplier initiative/Supplier_Capacity_Inputs.xlsx
+++ b/PVA second supplier initiative/Supplier_Capacity_Inputs.xlsx
@@ -932,13 +932,13 @@
       <rgbColor rgb="FF800000"/>
       <rgbColor rgb="FF008300"/>
       <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF459428"/>
+      <rgbColor rgb="FF7F7F7F"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF7F7F7F"/>
+      <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFBFBFBF"/>
       <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF889AAA"/>
-      <rgbColor rgb="FFA02B93"/>
+      <rgbColor rgb="FF8B8B8B"/>
+      <rgbColor rgb="FFE34948"/>
       <rgbColor rgb="FFF7F7F7"/>
       <rgbColor rgb="FFE7E7E7"/>
       <rgbColor rgb="FF660066"/>
@@ -959,7 +959,7 @@
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FFB3B3B3"/>
       <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FF8B8B8B"/>
+      <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF2A78D6"/>
       <rgbColor rgb="FF33CCCC"/>
@@ -974,7 +974,7 @@
       <rgbColor rgb="FF0B0B0B"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FFE34948"/>
+      <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF4A3AA7"/>
       <rgbColor rgb="FF404040"/>
     </indexedColors>
@@ -1305,29 +1305,6 @@
               </a:ln>
             </spPr>
           </marker>
-          <dPt>
-            <idx val="4"/>
-            <marker>
-              <symbol val="circle"/>
-              <size val="7"/>
-              <spPr>
-                <a:solidFill>
-                  <a:srgbClr val="0B0B0B"/>
-                </a:solidFill>
-                <a:ln w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                  <a:prstDash val="solid"/>
-                </a:ln>
-              </spPr>
-            </marker>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
           <dLbls>
             <dLbl>
               <idx val="4"/>
@@ -1984,29 +1961,6 @@
               </a:ln>
             </spPr>
           </marker>
-          <dPt>
-            <idx val="4"/>
-            <marker>
-              <symbol val="circle"/>
-              <size val="7"/>
-              <spPr>
-                <a:solidFill>
-                  <a:srgbClr val="0B0B0B"/>
-                </a:solidFill>
-                <a:ln w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                  <a:prstDash val="solid"/>
-                </a:ln>
-              </spPr>
-            </marker>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
           <dLbls>
             <dLbl>
               <idx val="4"/>
@@ -2686,29 +2640,6 @@
               </a:ln>
             </spPr>
           </marker>
-          <dPt>
-            <idx val="4"/>
-            <marker>
-              <symbol val="circle"/>
-              <size val="7"/>
-              <spPr>
-                <a:solidFill>
-                  <a:srgbClr val="0B0B0B"/>
-                </a:solidFill>
-                <a:ln w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                  <a:prstDash val="solid"/>
-                </a:ln>
-              </spPr>
-            </marker>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
           <val>
             <numRef>
               <f>'Chart Data'!$B$21:$F$21</f>
@@ -3275,29 +3206,6 @@
               </a:ln>
             </spPr>
           </marker>
-          <dPt>
-            <idx val="4"/>
-            <marker>
-              <symbol val="circle"/>
-              <size val="7"/>
-              <spPr>
-                <a:solidFill>
-                  <a:srgbClr val="0B0B0B"/>
-                </a:solidFill>
-                <a:ln w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                  <a:prstDash val="solid"/>
-                </a:ln>
-              </spPr>
-            </marker>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
           <dLbls>
             <dLbl>
               <idx val="4"/>
@@ -4205,29 +4113,6 @@
               </a:ln>
             </spPr>
           </marker>
-          <dPt>
-            <idx val="4"/>
-            <marker>
-              <symbol val="circle"/>
-              <size val="6"/>
-              <spPr>
-                <a:solidFill>
-                  <a:srgbClr val="999999"/>
-                </a:solidFill>
-                <a:ln w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                  <a:prstDash val="solid"/>
-                </a:ln>
-              </spPr>
-            </marker>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
           <dLbls>
             <dLbl>
               <idx val="4"/>
